--- a/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
+++ b/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Conflict Register" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cell Lineage'!$A$1:$F$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cell Lineage'!$A$1:$F$166</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F167"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Adolf Bollenbach, or his unlocated successors and assigns (65.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: Unresolved successors of Adolf Bollenbach (last proved record owner, WD 10/255, 01/31/1910) — chain gap remains unresolved (65.000000 NMA)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 65.000000 NMA residual vests in last traced record owner (WD 10/255); no chain-out located. Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: 65.000000 NMA residual vests in last traced record owner (WD 10/255); no chain-out located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: WD 10/255. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: C. B. Crook, Jr. (8.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: C. B. Crook, Jr. — last located record owner; no later conveyance located; current status not confirmed (8.000000 NMA)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Carole Faye Hanks (8.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: Carole Faye Hanks — last located record owner; no later conveyance located; current status not confirmed (8.000000 NMA)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Doris Marie Lenderman (8.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: Doris Marie Lenderman — last located record owner; no later conveyance located; current status not confirmed (8.000000 NMA)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: F. L. Randel and J. L. Randel, share and share alike (Wichita Falls, TX) (1.500000 NMA)</t>
+          <t>TRACT 1 estimated owner: F. L. Randel and J. L. Randel, share and share alike (Wichita Falls, TX) — last located record owner; no later conveyance located; current status not confirmed (1.500000 NMA)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 92/47; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 92/47; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 92/47. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Five issue of Charlie B. Crook (collective row - chained out) (0.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: Great Western (entity as shown on the reviewed face, img 1558) — last located record owner; no later conveyance located; current status not confirmed (10.000000 NMA)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Chained out: distributed individually per DECR 845/149-153 and 845/152 clause (h); retained at 0 NMA for audit. Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 367/632; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 367/632. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Great Western (entity as shown on the reviewed face, img 1558) (10.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: Ina Bell Bryan — last located record owner; no later conveyance located; current status not confirmed (8.000000 NMA)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 367/632; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Ina Bell Bryan (8.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: Jean Jenkins Shearer, Florence Jenkins Chunn and William Rundell Jenkins, JTWROS — last located record owner; no later conveyance located; current status not confirmed (2.000000 NMA)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 250/26; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 250/26. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Jean Jenkins Shearer, Florence Jenkins Chunn and William Rundell Jenkins, JTWROS (2.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: Mary Joyce Higgenbotham — last located record owner; no later conveyance located; current status not confirmed (8.000000 NMA)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 250/26; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Mary Joyce Higgenbotham (8.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: Unresolved probate beneficiaries under Decree 83/259 (Estate of Ellen W. Crook) — individual allocations not stated on the decree face (40.000000 NMA)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: 40.000000 NMA vests collectively per decree; individual allocations not stated on the face. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Beneficiaries of Ellen W. Crook (13 named, DECR 83/259) (40.000000 NMA)</t>
+          <t>TRACT 1 estimated owner: Unresolved record owner — grantee of the F. L. Randel 1.5-acre deed (img 1794); grantee name not read from the face (1.500000 NMA)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 40.000000 NMA vests collectively per decree; individual allocations not stated on the face. Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: holds 1.500000 NMA per the recorded deed; grantee name not extracted from the face. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>B17:G17</t>
+          <t>B23:G23</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>TRACT 1 estimated owner: Grantee of the F. L. Randel 1.5-acre deed (img 1794) (1.500000 NMA)</t>
+          <t>TRACT 2 estimated owner: B. E. Maddoux (stipulated residual) — last located record owner; no later conveyance located; current status not confirmed (10.000000 NMA)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: holds 1.500000 NMA per the recorded deed; grantee name not extracted from the face. Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>B22:G22</t>
+          <t>B24:G24</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: B. E. Maddoux (stipulated residual) (10.000000 NMA)</t>
+          <t>TRACT 2 estimated owner: D. H. Maddoux (stipulated residual) — last located record owner; no later conveyance located; current status not confirmed (10.000000 NMA)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>B23:G23</t>
+          <t>B25:G25</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: D. H. Maddoux (stipulated residual) (10.000000 NMA)</t>
+          <t>TRACT 2 estimated owner: E. C. (E. G.) Sanditen — last located record owner; no later conveyance located; current status not confirmed (7.500000 NMA)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/365 corr. 87/174; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/365 corr. 87/174. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>B24:G24</t>
+          <t>B26:G26</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: E. C. (E. G.) Sanditen (7.500000 NMA)</t>
+          <t>TRACT 2 estimated owner: Edna Mae Walker Revocable Trust dtd 05/21/1981 — last located record owner; no later conveyance located; current status not confirmed (0.416666 NMA)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/365 corr. 87/174; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>B25:G25</t>
+          <t>B27:G27</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Edna Mae Walker Revocable Trust dtd 05/21/1981 (0.416666 NMA)</t>
+          <t>TRACT 2 estimated owner: First National Bank &amp; Trust Co. of Tulsa, Trustee u/w Mylon C. Jacobs, Sr. — last located record owner; no later conveyance located; current status not confirmed (0.250000 NMA)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1287/42; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 312/700-704. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>B26:G26</t>
+          <t>B28:G28</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: First National Bank &amp; Trust Co. of Tulsa, Trustee u/w Mylon C. Jacobs, Sr. (0.250000 NMA)</t>
+          <t>TRACT 2 estimated owner: George T. Harrison, Jr. and Renata Harrison — last located record owner; no later conveyance located; current status not confirmed (0.100000 NMA)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/424; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/424. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>B27:G27</t>
+          <t>B29:G29</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: George T. Harrison, Jr. and Renata Harrison (0.100000 NMA)</t>
+          <t>TRACT 2 estimated owner: Herman Sanditen — last located record owner; no later conveyance located; current status not confirmed (7.500000 NMA)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/424; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/363; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/363. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>B28:G28</t>
+          <t>B30:G30</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Herman Sanditen (7.500000 NMA)</t>
+          <t>TRACT 2 estimated owner: J. F. Costello (Lindsay, OK) — last located record owner; no later conveyance located; current status not confirmed (5.000000 NMA)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/363; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/245; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/245. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>B29:G29</t>
+          <t>B31:G31</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: J. F. Costello (Lindsay, OK) (5.000000 NMA)</t>
+          <t>TRACT 2 estimated owner: Jack V. Walker Revocable Trust dtd 05/21/1981 — last located record owner; no later conveyance located; current status not confirmed (0.416666 NMA)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/245; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>B30:G30</t>
+          <t>B32:G32</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Jack V. Walker Revocable Trust dtd 05/21/1981 (0.416666 NMA)</t>
+          <t>TRACT 2 estimated owner: James M. Murray, Jr. — last located record owner; no later conveyance located; current status not confirmed (0.200000 NMA)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1287/42; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/428; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/428. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>B31:G31</t>
+          <t>B33:G33</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: James M. Murray, Jr. (0.200000 NMA)</t>
+          <t>TRACT 2 estimated owner: John Holbrook — last located record owner; no later conveyance located; current status not confirmed (0.100000 NMA)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/428; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/426; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/426. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>B32:G32</t>
+          <t>B34:G34</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: John Holbrook (0.100000 NMA)</t>
+          <t>TRACT 2 estimated owner: Julius Sanditen — last located record owner; no later conveyance located; current status not confirmed (7.500000 NMA)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/426; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/364; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/364. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1476,12 +1476,12 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>B33:G33</t>
+          <t>B35:G35</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Julius Sanditen (7.500000 NMA)</t>
+          <t>TRACT 2 estimated owner: Kershaw Properties — last located record owner; no later conveyance located; current status not confirmed (3.375000 NMA)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/364; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>B34:G34</t>
+          <t>B36:G36</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Kershaw Properties (3.375000 NMA)</t>
+          <t>TRACT 2 estimated owner: Louis Fenster — last located record owner; no later conveyance located; current status not confirmed (4.000000 NMA)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/366; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/366. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>B35:G35</t>
+          <t>B37:G37</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Louis Fenster (4.000000 NMA)</t>
+          <t>TRACT 2 estimated owner: Mathew Keck (Chicago) — last located record owner; no later conveyance located; current status not confirmed (1.000000 NMA)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/366; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 88/172; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/172. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>B36:G36</t>
+          <t>B38:G38</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Mathew Keck (Chicago) (1.000000 NMA)</t>
+          <t>TRACT 2 estimated owner: Robert A. Gannaway — last located record owner; no later conveyance located; current status not confirmed (3.375000 NMA)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 88/172; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>B37:G37</t>
+          <t>B39:G39</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Robert A. Gannaway (3.375000 NMA)</t>
+          <t>TRACT 2 estimated owner: Robert R. Lockwood, Jr. — last located record owner; no later conveyance located; current status not confirmed (0.250000 NMA)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/87; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/87. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1636,12 +1636,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>B38:G38</t>
+          <t>B40:G40</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Robert R. Lockwood, Jr. (0.250000 NMA)</t>
+          <t>TRACT 2 estimated owner: Sara M. Smith — last located record owner; no later conveyance located; current status not confirmed (0.100000 NMA)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/87; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/422; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/422. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>B39:G39</t>
+          <t>B41:G41</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Sara M. Smith (0.100000 NMA)</t>
+          <t>TRACT 2 estimated owner: Untraced successor interest in the Farrar N/2 NW/4 fee — connecting instrument not located (12.166667 NMA)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/422; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: 12.166667 NMA carried in the Farrar fee chain; connecting instrument not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>B40:G40</t>
+          <t>B42:G42</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Successors of the Farrar NW/4 fee (Farrar-to-Maddoux chain) (12.166667 NMA)</t>
+          <t>TRACT 2 estimated owner: Unresolved successors of Maurice Sanditen (index reference 92/468; later family instruments unread) (6.750000 NMA)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 12.166667 NMA carried in the Farrar fee chain; connecting instrument not located. Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: 6.750000 NMA per 92/468 (index) and later family instruments not read. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: 92/468. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1732,12 +1732,12 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>B41:G41</t>
+          <t>B47:G47</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>TRACT 2 estimated owner: Maurice Sanditen, or his successors and assigns (6.750000 NMA)</t>
+          <t>TRACT 3 estimated owner: Claud B. Hamill — last located record owner; no later conveyance located; current status not confirmed (40.000000 NMA)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 6.750000 NMA per 92/468 (index) and later family instruments not read. Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 86/21; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 86/21. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>B46:G46</t>
+          <t>B48:G48</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>TRACT 3 estimated owner: Claud B. Hamill (40.000000 NMA)</t>
+          <t>TRACT 3 estimated owner: Unresolved successors of G. B. and Ola Keathley — residue exposed by Decree P-76-78 (13.333333 NMA)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 86/21; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: 13.333333 NMA residue exposed by DECR P-76-78 vests in untraced Keathley successors. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>B47:G47</t>
+          <t>B49:G49</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>TRACT 3 estimated owner: Successors of G. B. and Ola Keathley (13.333333 NMA)</t>
+          <t>TRACT 3 estimated owner: J. A. Brescian — last located record owner; no later conveyance located; current status not confirmed (10.000000 NMA)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 13.333333 NMA residue exposed by DECR P-76-78 vests in untraced Keathley successors. Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/36; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/36. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>B48:G48</t>
+          <t>B50:G50</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>TRACT 3 estimated owner: J. A. Brescian (10.000000 NMA)</t>
+          <t>TRACT 3 estimated owner: Leo Keathley and La Wanda Keathley, H/W — last located record owner; no later conveyance located; current status not confirmed (2.222222 NMA)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/36; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR P-76-78, pages 349-350 (images 1546-1550). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1860,12 +1860,12 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>B49:G49</t>
+          <t>B51:G51</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>TRACT 3 estimated owner: Leo Keathley and La Wanda Keathley, H/W (2.222222 NMA)</t>
+          <t>TRACT 3 estimated owner: Milton Keathley and Inez Keathley, H/W — last located record owner; no later conveyance located; current status not confirmed (2.222222 NMA)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR P-76-78, pages 349-350 (images 1546-1550). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>B50:G50</t>
+          <t>B52:G52</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>TRACT 3 estimated owner: Milton Keathley and Inez Keathley, H/W (2.222222 NMA)</t>
+          <t>TRACT 3 estimated owner: Slemp Oil Company — last located record owner; no later conveyance located; current status not confirmed (10.000000 NMA)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 74/63; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 74/63. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>B51:G51</t>
+          <t>B53:G53</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>TRACT 3 estimated owner: Slemp Oil Company (10.000000 NMA)</t>
+          <t>TRACT 3 estimated owner: T. G. Le Grand and Juanita Le Grand, H/W — last located record owner; no later conveyance located; current status not confirmed (2.222222 NMA)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 74/63; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR P-76-78, pages 349-350 (images 1546-1550). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>B52:G52</t>
+          <t>B58:G58</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>TRACT 3 estimated owner: T. G. Le Grand and Juanita Le Grand, H/W (2.222222 NMA)</t>
+          <t>TRACT 4 estimated owner: B. E. Maddoux (stipulated residual) — last located record owner; no later conveyance located; current status not confirmed (10.000000 NMA)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -1988,12 +1988,12 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>B57:G57</t>
+          <t>B59:G59</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: B. E. Maddoux (stipulated residual) (10.000000 NMA)</t>
+          <t>TRACT 4 estimated owner: D. H. Maddoux (stipulated residual) — last located record owner; no later conveyance located; current status not confirmed (10.000000 NMA)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>B58:G58</t>
+          <t>B60:G60</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: D. H. Maddoux (stipulated residual) (10.000000 NMA)</t>
+          <t>TRACT 4 estimated owner: Edna Mae Walker Revocable Trust dtd 05/21/1981 — last located record owner; no later conveyance located; current status not confirmed (0.416666 NMA)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>B59:G59</t>
+          <t>B61:G61</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Edna Mae Walker Revocable Trust dtd 05/21/1981 (0.416666 NMA)</t>
+          <t>TRACT 4 estimated owner: First National Bank &amp; Trust Co. of Tulsa, Trustee u/w Mylon C. Jacobs, Sr. — last located record owner; no later conveyance located; current status not confirmed (1.000000 NMA)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1287/42; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 312/700-704. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2084,12 +2084,12 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>B60:G60</t>
+          <t>B62:G62</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: First National Bank &amp; Trust Co. of Tulsa, Trustee u/w Mylon C. Jacobs, Sr. (1.000000 NMA)</t>
+          <t>TRACT 4 estimated owner: George T. Harrison, Jr. and Renata Harrison — last located record owner; no later conveyance located; current status not confirmed (0.400000 NMA)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/424; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/424. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>B61:G61</t>
+          <t>B63:G63</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: George T. Harrison, Jr. and Renata Harrison (0.400000 NMA)</t>
+          <t>TRACT 4 estimated owner: Gertrude L. LaFortune, Jeanne L. Fair, Mary Ann L. Wilcox, J. A. LaFortune Jr. and Robert J. LaFortune, Co-Trustees u/w (in trust) — last located record owner; no later conveyance located; current status not confirmed (1.333334 NMA)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/424; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 333/239-248; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 333/239-248. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>B62:G62</t>
+          <t>B64:G64</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Gertrude L. LaFortune, Jeanne L. Fair, Mary Ann L. Wilcox, J. A. LaFortune Jr. and Robert J. LaFortune, Co-Trustees u/w (in trust) (1.333334 NMA)</t>
+          <t>TRACT 4 estimated owner: Helen Langer May (Palos Park, IL) — last located record owner; no later conveyance located; current status not confirmed (1.000000 NMA)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 333/239-248; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 88/174; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/174. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>B63:G63</t>
+          <t>B65:G65</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Helen Langer May (Palos Park, IL) (1.000000 NMA)</t>
+          <t>TRACT 4 estimated owner: Jack V. Walker Revocable Trust dtd 05/21/1981 — last located record owner; no later conveyance located; current status not confirmed (0.416666 NMA)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 88/174; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2212,12 +2212,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>B64:G64</t>
+          <t>B66:G66</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Jack V. Walker Revocable Trust dtd 05/21/1981 (0.416666 NMA)</t>
+          <t>TRACT 4 estimated owner: James M. Murray, Jr. — last located record owner; no later conveyance located; current status not confirmed (0.800000 NMA)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1287/42; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/428; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/428. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>B65:G65</t>
+          <t>B67:G67</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: James M. Murray, Jr. (0.800000 NMA)</t>
+          <t>TRACT 4 estimated owner: John Holbrook — last located record owner; no later conveyance located; current status not confirmed (0.400000 NMA)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/428; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/426; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/426. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>B66:G66</t>
+          <t>B68:G68</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: John Holbrook (0.400000 NMA)</t>
+          <t>TRACT 4 estimated owner: LaFortune Tung Oil Mill — last located record owner; no later conveyance located; current status not confirmed (1.333334 NMA)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/426; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 90/242; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 90/242. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2308,12 +2308,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>B67:G67</t>
+          <t>B69:G69</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: LaFortune Tung Oil Mill (1.333334 NMA)</t>
+          <t>TRACT 4 estimated owner: Mathew Keck (Chicago) — last located record owner; no later conveyance located; current status not confirmed (3.000000 NMA)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 90/242; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 88/172; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/172. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>B68:G68</t>
+          <t>B70:G70</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Mathew Keck (Chicago) (3.000000 NMA)</t>
+          <t>TRACT 4 estimated owner: Robert James LaFortune — last located record owner; no later conveyance located; current status not confirmed (1.333334 NMA)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 88/172; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 90/241; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 90/241. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>B69:G69</t>
+          <t>B71:G71</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Robert James LaFortune (1.333334 NMA)</t>
+          <t>TRACT 4 estimated owner: Robert R. Lockwood, Jr. — last located record owner; no later conveyance located; current status not confirmed (1.000000 NMA)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 90/241; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/87; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/87. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>B70:G70</t>
+          <t>B72:G72</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Robert R. Lockwood, Jr. (1.000000 NMA)</t>
+          <t>TRACT 4 estimated owner: Sara M. Smith — last located record owner; no later conveyance located; current status not confirmed (0.400000 NMA)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/87; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/422; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/422. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2436,12 +2436,12 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>B71:G71</t>
+          <t>B73:G73</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Sara M. Smith (0.400000 NMA)</t>
+          <t>TRACT 4 estimated owner: Seidenbach's (entity, 413 S. Main, Tulsa) — last located record owner; no later conveyance located; current status not confirmed (5.000000 NMA)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/422; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 90/153; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 90/153. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>B72:G72</t>
+          <t>B74:G74</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Seidenbach's (entity, 413 S. Main, Tulsa) (5.000000 NMA)</t>
+          <t>TRACT 4 estimated owner: T. D. Norris — last located record owner; no later conveyance located; current status not confirmed (5.000000 NMA)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 90/153; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/315; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/315. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>B73:G73</t>
+          <t>B75:G75</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: T. D. Norris (5.000000 NMA)</t>
+          <t>TRACT 4 estimated owner: The Heller Company — last located record owner; no later conveyance located; current status not confirmed (17.999999 NMA)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/315; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/222; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/222. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>B74:G74</t>
+          <t>B76:G76</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: The Heller Company (17.999999 NMA)</t>
+          <t>TRACT 4 estimated owner: Bettye Folmar Norris — last located record owner; no later conveyance located; current status not confirmed (5.000000 NMA)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/222; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 262/490-493 (P-71-473); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 262/490-493 (P-71-473). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>B75:G75</t>
+          <t>B77:G77</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Bettye Folmar Norris (5.000000 NMA)</t>
+          <t>TRACT 4 estimated owner: Untraced successor interest — Stevens-to-Maddoux chain; connecting instrument not located (14.166667 NMA)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 262/490-493 (P-71-473); EST.* Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: 14.166667 NMA carried in the Stevens chain; connecting instrument not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>B76:G76</t>
+          <t>B82:G82</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>TRACT 4 estimated owner: Successors of the Stevens interest (Stevens-to-Maddoux chain) (14.166667 NMA)</t>
+          <t>TRACT 5 estimated owner: C. R. Bennett (812 Palace Building, Tulsa) — last located record owner; no later conveyance located; current status not confirmed (40.000000 NMA)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 14.166667 NMA carried in the Stevens chain; connecting instrument not located. Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 81/194; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 81/194. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>B81:G81</t>
+          <t>B83:G83</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>TRACT 5 estimated owner: C. R. Bennett (812 Palace Building, Tulsa) (40.000000 NMA)</t>
+          <t>TRACT 5 estimated owner: Untraced successor interest — Stevens-to-LeGrand chain; connecting instrument not located (35.000000 NMA)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 81/194; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: 35.000000 NMA carried in the Stevens chain; connecting instrument not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>B82:G82</t>
+          <t>B84:G84</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>TRACT 5 estimated owner: Successors of the Stevens interest (Stevens-to-LeGrand chain) (35.000000 NMA)</t>
+          <t>TRACT 5 estimated owner: W. F. Palmer (Wichita Falls, TX) — last located record owner; no later conveyance located; current status not confirmed (5.000000 NMA)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 35.000000 NMA carried in the Stevens chain; connecting instrument not located. Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 92/115 (previously mis-cited 92/120); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 92/115 (previously mis-cited 92/120). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>B83:G83</t>
+          <t>B89:G89</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>TRACT 5 estimated owner: W. F. Palmer (Wichita Falls, TX) (5.000000 NMA)</t>
+          <t>TRACT 6 estimated owner: Carlene Stewart — last located record owner; no later conveyance located; current status not confirmed (7.993200 NMA)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 92/115 (previously mis-cited 92/120); EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1063/166; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1063/166. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>B88:G88</t>
+          <t>B90:G90</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Carlene Stewart (7.993200 NMA)</t>
+          <t>TRACT 6 estimated owner: Unresolved successors of Cora B. Garrett and S. A. Garrett (OGL 1 lessors of record) — succession untraced (27.674000 NMA)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1063/166; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: 27.674000 NMA residual vests in OGL 1 lessors of record; succession untraced. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -2756,12 +2756,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>B89:G89</t>
+          <t>B91:G91</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Cora B. Garrett and S. A. Garrett, or unlocated successors (27.674000 NMA)</t>
+          <t>TRACT 6 estimated owner: E. C. (E. G.) Sanditen — last located record owner; no later conveyance located; current status not confirmed (3.750000 NMA)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 27.674000 NMA residual vests in OGL 1 lessors of record; succession untraced. Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/365 corr. 87/174; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/365 corr. 87/174. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -2788,12 +2788,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>B90:G90</t>
+          <t>B92:G92</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: E. C. (E. G.) Sanditen (3.750000 NMA)</t>
+          <t>TRACT 6 estimated owner: First National Bank &amp; Trust Co. of Tulsa, Trustee u/w Mylon C. Jacobs, Sr. — last located record owner; no later conveyance located; current status not confirmed (0.500000 NMA)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/365 corr. 87/174; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 312/700-704. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -2820,12 +2820,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>B91:G91</t>
+          <t>B93:G93</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: First National Bank &amp; Trust Co. of Tulsa, Trustee u/w Mylon C. Jacobs, Sr. (0.500000 NMA)</t>
+          <t>TRACT 6 estimated owner: George T. Harrison, Jr. and Renata Harrison — last located record owner; no later conveyance located; current status not confirmed (0.200000 NMA)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/424; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/424. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>B92:G92</t>
+          <t>B94:G94</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: George T. Harrison, Jr. and Renata Harrison (0.200000 NMA)</t>
+          <t>TRACT 6 estimated owner: Herman Sanditen — last located record owner; no later conveyance located; current status not confirmed (3.750000 NMA)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/424; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/363; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/363. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>B93:G93</t>
+          <t>B95:G95</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Herman Sanditen (3.750000 NMA)</t>
+          <t>TRACT 6 estimated owner: J. F. Costello (Lindsay, OK) — last located record owner; no later conveyance located; current status not confirmed (5.000000 NMA)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/363; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/244; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/244. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>B94:G94</t>
+          <t>B96:G96</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: J. F. Costello (Lindsay, OK) (5.000000 NMA)</t>
+          <t>TRACT 6 estimated owner: James M. Murray, Jr. — last located record owner; no later conveyance located; current status not confirmed (0.400000 NMA)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/244; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/428; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/428. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -2948,12 +2948,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>B95:G95</t>
+          <t>B97:G97</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: James M. Murray, Jr. (0.400000 NMA)</t>
+          <t>TRACT 6 estimated owner: John Holbrook — last located record owner; no later conveyance located; current status not confirmed (0.200000 NMA)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/428; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/426; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/426. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -2980,12 +2980,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>B96:G96</t>
+          <t>B98:G98</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: John Holbrook (0.200000 NMA)</t>
+          <t>TRACT 6 estimated owner: Joseph Ervin Godwin, III (suffix II/III uncertain) — last located record owner; no later conveyance located; current status not confirmed (0.666600 NMA)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/426; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1090/94; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1090/94. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>B97:G97</t>
+          <t>B99:G99</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Joseph Ervin Godwin, III (suffix II/III uncertain) (0.666600 NMA)</t>
+          <t>TRACT 6 estimated owner: Julius Sanditen — last located record owner; no later conveyance located; current status not confirmed (3.750000 NMA)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1090/94; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/364; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/364. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>B98:G98</t>
+          <t>B100:G100</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Julius Sanditen (3.750000 NMA)</t>
+          <t>TRACT 6 estimated owner: Kershaw Properties — last located record owner; no later conveyance located; current status not confirmed (3.375000 NMA)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/364; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>B99:G99</t>
+          <t>B101:G101</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Kershaw Properties (3.375000 NMA)</t>
+          <t>TRACT 6 estimated owner: Louis Fenster — last located record owner; no later conveyance located; current status not confirmed (2.000000 NMA)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 85/366; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/366. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>B100:G100</t>
+          <t>B102:G102</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Louis Fenster (2.000000 NMA)</t>
+          <t>TRACT 6 estimated owner: Mathew Keck (Chicago) — last located record owner; no later conveyance located; current status not confirmed (2.000000 NMA)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/366; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 88/172; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/172. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>B101:G101</t>
+          <t>B103:G103</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Mathew Keck (Chicago) (2.000000 NMA)</t>
+          <t>TRACT 6 estimated owner: Millard E. Kuykendall — last located record owner; no later conveyance located; current status not confirmed (1.333200 NMA)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 88/172; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1063/164; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1063/164. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>B102:G102</t>
+          <t>B104:G104</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Millard E. Kuykendall (1.333200 NMA)</t>
+          <t>TRACT 6 estimated owner: R. E. Fowler and Sue Fowler; John R. Fowler and Louise Fowler (grantees collectively per the face) — last located record owner; no later conveyance located; current status not confirmed (6.333200 NMA)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1063/164; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1423/148; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1423/148. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>B103:G103</t>
+          <t>B105:G105</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: R. E. Fowler and Sue Fowler; John R. Fowler and Louise Fowler (grantees collectively per the face) (6.333200 NMA)</t>
+          <t>TRACT 6 estimated owner: Robert A. Gannaway — last located record owner; no later conveyance located; current status not confirmed (3.375000 NMA)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1423/148; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3236,12 +3236,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>B104:G104</t>
+          <t>B106:G106</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Robert A. Gannaway (3.375000 NMA)</t>
+          <t>TRACT 6 estimated owner: Robert R. Lockwood, Jr. — last located record owner; no later conveyance located; current status not confirmed (0.500000 NMA)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/87; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/87. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>B105:G105</t>
+          <t>B107:G107</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Robert R. Lockwood, Jr. (0.500000 NMA)</t>
+          <t>TRACT 6 estimated owner: Royice Roberts and Pauline Roberts, JTWROS — last located record owner; no later conveyance located; current status not confirmed (1.333200 NMA)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/87; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1063/164; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1063/164. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>B106:G106</t>
+          <t>B108:G108</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Royice Roberts and Pauline Roberts, JTWROS (1.333200 NMA)</t>
+          <t>TRACT 6 estimated owner: Sara M. Smith — last located record owner; no later conveyance located; current status not confirmed (0.200000 NMA)</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1063/164; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 89/422; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/422. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>B107:G107</t>
+          <t>B109:G109</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Sara M. Smith (0.200000 NMA)</t>
+          <t>TRACT 6 estimated owner: Timothy Adrian Godwin — last located record owner; no later conveyance located; current status not confirmed (0.666600 NMA)</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/422; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 1090/95 (face stamp; index reads 96); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1090/95 (face stamp. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>B108:G108</t>
+          <t>B110:G110</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Timothy Adrian Godwin (0.666600 NMA)</t>
+          <t>TRACT 6 estimated owner: Bettye Folmar Norris — last located record owner; no later conveyance located; current status not confirmed (5.000000 NMA)</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1090/95 (face stamp; index reads 96); EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: DECR 262/490-493 (P-71-473); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 262/490-493 (P-71-473). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>B109:G109</t>
+          <t>B115:G115</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>TRACT 6 estimated owner: Bettye Folmar Norris (5.000000 NMA)</t>
+          <t>TRACT 7 estimated owner: C. R. Bennett (812 Palace Building, Tulsa) — last located record owner; no later conveyance located; current status not confirmed (40.000000 NMA)</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 262/490-493 (P-71-473); EST.* Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 81/194; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 81/194. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>B114:G114</t>
+          <t>B116:G116</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>TRACT 7 estimated owner: C. R. Bennett (812 Palace Building, Tulsa) (40.000000 NMA)</t>
+          <t>TRACT 7 estimated owner: Unresolved successors of S. A. Garrett (last proved record owner) — chain-out not located (35.000000 NMA)</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 81/194; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>ASSUMED: 35.000000 NMA residual vests in last record owner; Garrett chain-out not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>B115:G115</t>
+          <t>B117:G117</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>TRACT 7 estimated owner: S. A. Garrett, or his unlocated successors and assigns (35.000000 NMA)</t>
+          <t>TRACT 7 estimated owner: W. F. Palmer (Wichita Falls, TX) — last located record owner; no later conveyance located; current status not confirmed (5.000000 NMA)</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 35.000000 NMA residual vests in last record owner; Garrett chain-out not located. Current status is not confirmed through the report effective date.</t>
+          <t>EST. last located record owner; Vested: MD 92/115; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 92/115. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -3487,32 +3487,32 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Title </t>
+          <t>OGL</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>B116:G116</t>
+          <t>A2:AB2</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>TRACT 7 estimated owner: W. F. Palmer (Wichita Falls, TX) (5.000000 NMA)</t>
+          <t>OGL 63/33 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>MT/V7</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 92/115; EST.* Current status is not confirmed through the report effective date.</t>
+          <t>Book/Page 63/33; Img 0353</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Estimated last-located record owner; current vesting and lease status qualified</t>
+          <t>HBP not independently confirmed; assumed potentially effective</t>
         </is>
       </c>
     </row>
@@ -3524,12 +3524,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>A2:AB2</t>
+          <t>A3:AB3</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>OGL 63/33 historic lease terms and qualified status</t>
+          <t>OGL 264/345 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 63/33; Img 0353</t>
+          <t>Book/Page 264/345; Imgs 1197-98</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>HBP not independently confirmed; assumed potentially effective</t>
+          <t>HBP not independently confirmed; recital supports assumed effectiveness</t>
         </is>
       </c>
     </row>
@@ -3556,27 +3556,27 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>A3:AB3</t>
+          <t>A4:AB4</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>OGL 264/345 historic lease terms and qualified status</t>
+          <t>OGL 307/31 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>MT/V7</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 264/345; Imgs 1197-98</t>
+          <t>Book/Page 307/31; Imgs 1372</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>HBP not independently confirmed; recital supports assumed effectiveness</t>
+          <t>Status not determined; HBP not independently confirmed</t>
         </is>
       </c>
     </row>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>A4:AB4</t>
+          <t>A5:AB5</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>OGL 307/31 historic lease terms and qualified status</t>
+          <t>OGL 340/302 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 307/31; Imgs 1372</t>
+          <t>Book/Page 340/302; Imgs 1522-23</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>A5:AB5</t>
+          <t>A6:AB6</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>OGL 340/302 historic lease terms and qualified status</t>
+          <t>OGL 340/304 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 340/302; Imgs 1522-23</t>
+          <t>Book/Page 340/304; Imgs 1524-25</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>A6:AB6</t>
+          <t>A7:AB7</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>OGL 340/304 historic lease terms and qualified status</t>
+          <t>OGL 340/323 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -3667,7 +3667,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 340/304; Imgs 1524-25</t>
+          <t>Book/Page 340/323; Imgs 1526-27</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>A7:AB7</t>
+          <t>A8:AB8</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>OGL 340/323 historic lease terms and qualified status</t>
+          <t>OGL 342/564 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 340/323; Imgs 1526-27</t>
+          <t>Book/Page 342/564; Imgs 1542-43</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>A8:AB8</t>
+          <t>A9:AB9</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>OGL 342/564 historic lease terms and qualified status</t>
+          <t>OGL 342/566 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 342/564; Imgs 1542-43</t>
+          <t>Book/Page 342/566; Imgs 1544-45</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -3748,12 +3748,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>A9:AB9</t>
+          <t>A10:AB10</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>OGL 342/566 historic lease terms and qualified status</t>
+          <t>OGL 352/719 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 342/566; Imgs 1544-45</t>
+          <t>Book/Page 352/719; Imgs 1552-53</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>A10:AB10</t>
+          <t>A11:AB11</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>OGL 352/719 historic lease terms and qualified status</t>
+          <t>OGL 352/721 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 352/719; Imgs 1552-53</t>
+          <t>Book/Page 352/721; Imgs 1554-55</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>A11:AB11</t>
+          <t>A12:AB12</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>OGL 352/721 historic lease terms and qualified status</t>
+          <t>OGL 376/369 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 352/721; Imgs 1554-55</t>
+          <t>Book/Page 376/369; Imgs 1569-70</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -3844,22 +3844,22 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>A12:AB12</t>
+          <t>A13:AB13</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>OGL 376/369 historic lease terms and qualified status</t>
+          <t>OGL 332/74-75 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>V7</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 376/369; Imgs 1569-70</t>
+          <t>Book/Page 332/74-75; Imgs 1457-58</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -3876,22 +3876,22 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>A13:AB13</t>
+          <t>A14:AB14</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>OGL 332/74-75 historic lease terms and qualified status</t>
+          <t>OGL 341/538 historic lease terms and qualified status</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>V7</t>
+          <t>FV/LC</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 332/74-75; Imgs 1457-58</t>
+          <t>Book/Page 341/538; Recited imgs 1568/1812/2031/2300</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -3903,32 +3903,32 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>OGL</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>A14:AB14</t>
+          <t>A104:K104</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>OGL 341/538 historic lease terms and qualified status</t>
+          <t>Added missing Section 32 chain lead 1016/7</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>FV/LC</t>
+          <t>V7, V10</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Book/Page 341/538; Recited imgs 1568/1812/2031/2300</t>
+          <t>1016 series; index lead, face not held</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Status not determined; HBP not independently confirmed</t>
+          <t>Locator/qualified evidence; full instrument required</t>
         </is>
       </c>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>A104:K104</t>
+          <t>A105:K105</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/7</t>
+          <t>Added missing Section 32 chain lead 1016/13</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>A105:K105</t>
+          <t>A106:K106</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/13</t>
+          <t>Added missing Section 32 chain lead 1016/18</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>A106:K106</t>
+          <t>A107:K107</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/18</t>
+          <t>Added missing Section 32 chain lead 1016/25</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>A107:K107</t>
+          <t>A108:K108</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/25</t>
+          <t>Added missing Section 32 chain lead 1016/29</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>A108:K108</t>
+          <t>A109:K109</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/29</t>
+          <t>Added missing Section 32 chain lead 1016/33</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>A109:K109</t>
+          <t>A110:K110</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/33</t>
+          <t>Added missing Section 32 chain lead 1016/90</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -4132,12 +4132,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>A110:K110</t>
+          <t>A111:K111</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/90</t>
+          <t>Added missing Section 32 chain lead 1697/236</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>1016 series; index lead, face not held</t>
+          <t>Recorded-face lead; required bridge into modern chain</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -4159,32 +4159,32 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Runsheet</t>
+          <t>Tract 1</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>A111:K111</t>
+          <t>A5:H5</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1697/236</t>
+          <t>PAT Patent 3/469 — Sovereign inception; no mineral reservation apparent</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>FV, V7, V10, MT</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Recorded-face lead; required bridge into modern chain</t>
+          <t>P-001 / Img 0003</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Locator/qualified evidence; full instrument required</t>
+          <t>98%</t>
         </is>
       </c>
     </row>
@@ -4196,12 +4196,12 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A6:H6</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>PAT Patent 3/469 — Sovereign inception; no mineral reservation apparent</t>
+          <t>WD Roger Mills 11/214 — NE/4 fee; no reservation apparent</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>P-001 / Img 0003</t>
+          <t>V7 direct-face register</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A7:H7</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>WD Roger Mills 11/214 — NE/4 fee; no reservation apparent</t>
+          <t>WD 10/255 — Fee to Adolf; downstream chain incomplete</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A8:H8</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>WD 10/255 — Fee to Adolf; downstream chain incomplete</t>
+          <t>DECR 83/259 — Collective mineral vesting; allocations require decree</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>V7 direct-face register</t>
+          <t>V7 probate extraction</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A9:H9</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>DECR 83/259 — Collective mineral vesting; allocations require decree</t>
+          <t>DECR 845/150-157 — Five 8-NMA estimated last-located interests</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -4312,7 +4312,7 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>High quantum / current status open</t>
         </is>
       </c>
     </row>
@@ -4324,12 +4324,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A10:H10</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>DECR 845/150-157 — Five 8-NMA estimated last-located interests</t>
+          <t>MD 92/47 — 1.5 NMA each per deed; later one grantee unextracted</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>V7 probate extraction</t>
+          <t>V7 direct-face register</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>High quantum / current status open</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -4356,12 +4356,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>A10:H10</t>
+          <t>A11:H11</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>MD 92/47 — 1.5 NMA each per deed; later one grantee unextracted</t>
+          <t>MD 367/632 — 10 NMA; competing 267/638 out-conveyance must be resolved</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -4376,24 +4376,24 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Tract 1</t>
+          <t>Tract 2</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>A11:H11</t>
+          <t>A5:H5</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>MD 367/632 — 10 NMA; competing 267/638 out-conveyance must be resolved</t>
+          <t>FR Final Receiver Receipt 3894 — Earliest located NW/4 evidence; patent not located</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>V7 direct-face register</t>
+          <t>P-003 / Img 0005</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>90% identity / 0% patent</t>
         </is>
       </c>
     </row>
@@ -4420,12 +4420,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A6:H6</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>FR Final Receiver Receipt 3894 — Earliest located NW/4 evidence; patent not located</t>
+          <t>STIP 153/161-162 — Recorded residual quantum used for estimated ending schedule</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>P-003 / Img 0005</t>
+          <t>V7 title register</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>90% identity / 0% patent</t>
+          <t>Medium-high</t>
         </is>
       </c>
     </row>
@@ -4452,12 +4452,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A7:H7</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>STIP 153/161-162 — Recorded residual quantum used for estimated ending schedule</t>
+          <t>MD/ORDER 85/363-366; 311/817-828 — Estimated last-located mineral interests</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Medium-high</t>
+          <t>Varies; current status open</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A8:H8</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>MD/ORDER 85/363-366; 311/817-828 — Estimated last-located mineral interests</t>
+          <t>DECR P-76-78 — Decree allocation incomplete; 13.333333-NMA residual assumed</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Varies; current status open</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4516,12 +4516,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A9:H9</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>DECR P-76-78 — Decree allocation incomplete; 13.333333-NMA residual assumed</t>
+          <t>OGL 340/323 — N/2 NW/4 plus N/2 SW/4; no current HBP conclusion</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -4531,29 +4531,29 @@
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>V7 title register</t>
+          <t>Direct face</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High terms / open status</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Tract 2</t>
+          <t>Tract 3</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A5:H5</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>OGL 340/323 — N/2 NW/4 plus N/2 SW/4; no current HBP conclusion</t>
+          <t>FR Final Receiver Receipt 3895 — Earliest located SW/4 evidence; patent not located</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Direct face</t>
+          <t>P-004 / Img 0006</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>High terms / open status</t>
+          <t>90% identity / 0% patent</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A6:H6</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>FR Final Receiver Receipt 3895 — Earliest located SW/4 evidence; patent not located</t>
+          <t>MD 81/194 — 40 NMA in S/2 SW/4 ending schedule</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>P-004 / Img 0006</t>
+          <t>V7 title register</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>90% identity / 0% patent</t>
+          <t>Medium; current status open</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A7:H7</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>MD 81/194 — 40 NMA in S/2 SW/4 ending schedule</t>
+          <t>MD/DECR 85/222; 262/490-493 — Estimated last-located interests</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Medium; current status open</t>
+          <t>Varies</t>
         </is>
       </c>
     </row>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A8:H8</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>MD/DECR 85/222; 262/490-493 — Estimated last-located interests</t>
+          <t>OGL 340/302; 340/304; 342/564; 342/566 — Overlapping N/2 SW/4 leases; not additive</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>V7 title register</t>
+          <t>Direct faces</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>High terms / open status</t>
         </is>
       </c>
     </row>
@@ -4676,12 +4676,12 @@
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A9:H9</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>OGL 340/302; 340/304; 342/564; 342/566 — Overlapping N/2 SW/4 leases; not additive</t>
+          <t>ASG 872/279 — Top Morrow-19,480 ft; ORRIs reserved; modern bridge open</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -4691,29 +4691,29 @@
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Direct faces</t>
+          <t>Direct images</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>High terms / open status</t>
+          <t>98% historic / open current</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Tract 3</t>
+          <t>Tract 4</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A5:H5</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>ASG 872/279 — Top Morrow-19,480 ft; ORRIs reserved; modern bridge open</t>
+          <t>FR Final Receiver Receipt — Earliest located SE/4 evidence; Biggs/Bigge patent remains missing</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>Direct images</t>
+          <t>P-002 / Img 0004</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>98% historic / open current</t>
+          <t>90% identity / 0% patent</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A6:H6</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>FR Final Receiver Receipt — Earliest located SE/4 evidence; Biggs/Bigge patent remains missing</t>
+          <t>OGL 63/33 — E/2 SE/4, 1/8 royalty, 10-year term; present status open</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>P-002 / Img 0004</t>
+          <t>Direct face</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>90% identity / 0% patent</t>
+          <t>98% terms</t>
         </is>
       </c>
     </row>
@@ -4772,12 +4772,12 @@
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A7:H7</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>OGL 63/33 — E/2 SE/4, 1/8 royalty, 10-year term; present status open</t>
+          <t>ASG 244/432 — Historic 63/33 assignment branch</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Direct face</t>
+          <t>Direct image</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>98% terms</t>
+          <t>96%</t>
         </is>
       </c>
     </row>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A8:H8</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>ASG 244/432 — Historic 63/33 assignment branch</t>
+          <t>WB ASG 845/47 — Pearl wellbore 11,100-19,480 ft; 1/8 ORRI</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>98% historic</t>
         </is>
       </c>
     </row>
@@ -4836,12 +4836,12 @@
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A9:H9</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>WB ASG 845/47 — Pearl wellbore 11,100-19,480 ft; 1/8 ORRI</t>
+          <t>OGL 307/31 — W/2 SE/4 and S/2 SW/4; present status open</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
@@ -4851,29 +4851,29 @@
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Direct image</t>
+          <t>Direct face</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>98% historic</t>
+          <t>98% terms</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Tract 4</t>
+          <t>Tract 5</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A5:H5</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>OGL 307/31 — W/2 SE/4 and S/2 SW/4; present status open</t>
+          <t>ASG 1697/236 — Scheduled predecessor lead; full Exhibit A controls</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
@@ -4883,12 +4883,12 @@
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Direct face</t>
+          <t>Recorded face / Exhibit A required</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>98% terms</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A6:H6</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>ASG 1697/236 — Scheduled predecessor lead; full Exhibit A controls</t>
+          <t>ASG 2340/490 — Full-section indexed; missing Tapstone/asset bridge schedules</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
@@ -4915,12 +4915,12 @@
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Recorded face / Exhibit A required</t>
+          <t>Index / schedule missing</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High metadata / low scope</t>
         </is>
       </c>
     </row>
@@ -4932,12 +4932,12 @@
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A7:H7</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>ASG 2340/490 — Full-section indexed; missing Tapstone/asset bridge schedules</t>
+          <t>ASG 2371/470-494 — 51.25%/48.75% transaction branches; not current WI</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Index / schedule missing</t>
+          <t>Index / instrument partial</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>High metadata / low scope</t>
+          <t>High parties / low asset quantum</t>
         </is>
       </c>
     </row>
@@ -4964,12 +4964,12 @@
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A8:H8</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>ASG 2371/470-494 — 51.25%/48.75% transaction branches; not current WI</t>
+          <t>MERGER 2389/500-580 — Corporate consolidation; asset-specific effect open</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Index / instrument partial</t>
+          <t>Index / certificate missing</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>High parties / low asset quantum</t>
+          <t>High metadata</t>
         </is>
       </c>
     </row>
@@ -4996,12 +4996,12 @@
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A9:H9</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>MERGER 2389/500-580 — Corporate consolidation; asset-specific effect open</t>
+          <t>CONV 2395/415-464 — OK48147.001.1 identified; allocation/estate/depth blank</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
@@ -5011,12 +5011,12 @@
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Index / certificate missing</t>
+          <t>Reviewed asset line 2395/462</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>High metadata</t>
+          <t>High asset identity / low quantum</t>
         </is>
       </c>
     </row>
@@ -5028,12 +5028,12 @@
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A10:H10</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>CONV 2395/415-464 — OK48147.001.1 identified; allocation/estate/depth blank</t>
+          <t>CONV 2400/551-567 — Latest supported named claimant; exact current WI/NRI open</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Reviewed asset line 2395/462</t>
+          <t>Reviewed asset line 2400/566</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -5060,12 +5060,12 @@
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>A10:H10</t>
+          <t>A11:H11</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>CONV 2400/551-567 — Latest supported named claimant; exact current WI/NRI open</t>
+          <t>AGMT 2476/121-130 — Agreement, not facial conveyance; current vesting effect open</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -5075,44 +5075,44 @@
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Reviewed asset line 2400/566</t>
+          <t>Index/public metadata</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>High asset identity / low quantum</t>
+          <t>High metadata / low title effect</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Tract 5</t>
+          <t>WI 1</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>A11:H11</t>
+          <t>A5:H5</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>AGMT 2476/121-130 — Agreement, not facial conveyance; current vesting effect open</t>
+          <t>Historic scheduled predecessor lead</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>LC, V7, V10, FV</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Index/public metadata</t>
+          <t>1697/236</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>High metadata / low title effect</t>
+          <t>Full Exhibit A required</t>
         </is>
       </c>
     </row>
@@ -5124,12 +5124,12 @@
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A6:H6</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Historic scheduled predecessor lead</t>
+          <t>Potential bridge branch</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>1697/236</t>
+          <t>2340/403</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Full Exhibit A required</t>
+          <t>Missing Tapstone schedule/bridge</t>
         </is>
       </c>
     </row>
@@ -5156,12 +5156,12 @@
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A7:H7</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Potential bridge branch</t>
+          <t>Principal indexed predecessor</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>2340/403</t>
+          <t>2340/490</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Missing Tapstone schedule/bridge</t>
+          <t>Asset schedule absent</t>
         </is>
       </c>
     </row>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A8:H8</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Principal indexed predecessor</t>
+          <t>Keep branches separate</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>2340/490</t>
+          <t>2371/470-494</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Asset schedule absent</t>
+          <t>Not current Section 32 WI</t>
         </is>
       </c>
     </row>
@@ -5220,12 +5220,12 @@
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A9:H9</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Keep branches separate</t>
+          <t>Merger path</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>2371/470-494</t>
+          <t>2389/500-580</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Not current Section 32 WI</t>
+          <t>Certificate and schedules absent</t>
         </is>
       </c>
     </row>
@@ -5252,12 +5252,12 @@
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A10:H10</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Merger path</t>
+          <t>Asset identity supported</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>2389/500-580</t>
+          <t>2395/415-464</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Certificate and schedules absent</t>
+          <t>Estate/depth/quantum blank</t>
         </is>
       </c>
     </row>
@@ -5284,12 +5284,12 @@
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>A10:H10</t>
+          <t>A11:H11</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Asset identity supported</t>
+          <t>Latest supported named claimant</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>2395/415-464</t>
+          <t>2400/551-567</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Estate/depth/quantum blank</t>
+          <t>Later filings and exact quantum open</t>
         </is>
       </c>
     </row>
@@ -5316,12 +5316,12 @@
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>A11:H11</t>
+          <t>A12:H12</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Latest supported named claimant</t>
+          <t>Later context only</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -5331,44 +5331,44 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>2400/551-567</t>
+          <t>2451/4-23; 2476/121</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Later filings and exact quantum open</t>
+          <t>Read complete instruments</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>WI 1</t>
+          <t>WI 2</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>A12:H12</t>
+          <t>A5:H5</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Later context only</t>
+          <t>Historic only; survival open</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>LC, V7, V10, FV</t>
+          <t>FV, V7, V10, MT</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>2451/4-23; 2476/121</t>
+          <t>502/267</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Read complete instruments</t>
+          <t>Payout, reversion and releases</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A6:H6</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Historic only; survival open</t>
+          <t>Historic allocation only</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>502/267</t>
+          <t>509/220</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Payout, reversion and releases</t>
+          <t>Prove baseline and successors</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A7:H7</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Historic allocation only</t>
+          <t>Historic only; status open</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>509/220</t>
+          <t>845/47</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Prove baseline and successors</t>
+          <t>Read unrecorded agreement and releases</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A8:H8</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Historic only; status open</t>
+          <t>Historic only; bridge open</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>845/47</t>
+          <t>872/279</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Read unrecorded agreement and releases</t>
+          <t>Complete instrument and 1984 agreement</t>
         </is>
       </c>
     </row>
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A9:H9</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Historic only; bridge open</t>
+          <t>Nemo-dat/source-title defect</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>872/279</t>
+          <t>1014/75</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Complete instrument and 1984 agreement</t>
+          <t>Prove assignor WI source</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A10:H10</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Nemo-dat/source-title defect</t>
+          <t>Separate branch; do not blend</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>1014/75</t>
+          <t>2183/174; 2185/639</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Prove assignor WI source</t>
+          <t>Read complete exhibits and legal</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>A10:H10</t>
+          <t>A11:H11</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Separate branch; do not blend</t>
+          <t>Parallel portfolio branch</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -5555,44 +5555,44 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>2183/174; 2185/639</t>
+          <t>2185/639; 2225/1; 2415/328</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Read complete exhibits and legal</t>
+          <t>Reconcile Teocalli carve and schedules</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>WI 2</t>
+          <t>Well 1</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>A11:H11</t>
+          <t>A3:Q3</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Parallel portfolio branch</t>
+          <t>Cora Garrett C-310 / 35-009-00075</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>2185/639; 2225/1; 2415/328</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Reconcile Teocalli carve and schedules</t>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
         </is>
       </c>
     </row>
@@ -5604,12 +5604,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>A3:Q3</t>
+          <t>A4:Q4</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Cora Garrett C-310 / 35-009-00075</t>
+          <t>Crook 1-32 / 35-009-20312</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>No rolling-12-month OTC rows (PUN 009-066620-0-0000, Active, 640 ac, still lists BP). AC/DRY under Complete Oil &amp; Gas Services LLC; Latigo-to-Complete Form 1073MW approved 12/3/2025 (Crook first of 38 wells). AC proves an open wellbore — NOT production or HBP.</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>A4:Q4</t>
+          <t>A5:Q5</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Crook 1-32 / 35-009-20312</t>
+          <t>Pearl 1-32 / 35-009-20605</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>No rolling-12-month OTC rows (PUN 009-066620-0-0000, Active, 640 ac, still lists BP). AC/DRY under Complete Oil &amp; Gas Services LLC; Latigo-to-Complete Form 1073MW approved 12/3/2025 (Crook first of 38 wells). AC proves an open wellbore — NOT production or HBP.</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>A5:Q5</t>
+          <t>A6:Q6</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Pearl 1-32 / 35-009-20605</t>
+          <t>Legrand 1-32 / 35-009-20738</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>A6:Q6</t>
+          <t>A7:Q7</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Legrand 1-32 / 35-009-20738</t>
+          <t>JGL 1-32 / 35-009-21072</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>Gas reported 7/2025-4/2026; 4/2026 = 2,367 MCF (OTC PUN 009-101800-0-0000, reported by NextEra Energy Marketing). Production fact only — HBP not concluded.</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>A7:Q7</t>
+          <t>A8:Q8</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>JGL 1-32 / 35-009-21072</t>
+          <t>Hanks Crook 1-32 / 35-009-21085</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Gas reported 7/2025-4/2026; 4/2026 = 2,367 MCF (OTC PUN 009-101800-0-0000, reported by NextEra Energy Marketing). Production fact only — HBP not concluded.</t>
+          <t>Active PUN returned no rolling-12-month rows on 7/9/2026.</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>A8:Q8</t>
+          <t>A9:Q9</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Hanks Crook 1-32 / 35-009-21085</t>
+          <t>Crook-Legrand 1-32 / 35-009-21166</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Active PUN returned no rolling-12-month rows on 7/9/2026.</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>A9:Q9</t>
+          <t>A10:Q10</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Crook-Legrand 1-32 / 35-009-21166</t>
+          <t>Legrand 1-32 / 35-009-21236</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>A10:Q10</t>
+          <t>A11:Q11</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Legrand 1-32 / 35-009-21236</t>
+          <t>Katie 1-32 / 35-009-21245</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>A11:Q11</t>
+          <t>A12:Q12</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Katie 1-32 / 35-009-21245</t>
+          <t>Legrand 2-32 / 35-009-21258</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>A12:Q12</t>
+          <t>A13:Q13</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Legrand 2-32 / 35-009-21258</t>
+          <t>Twin 1-32 / 35-009-21391</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>A13:Q13</t>
+          <t>A14:Q14</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Twin 1-32 / 35-009-21391</t>
+          <t>Carlson 32-11-25 12H / 35-009-21893</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>Gas through 5/2026; 5/2026 = 2,113 MCF (OTC PUN 009-211663-0-0000, Active, 640 ac). OTC displays API 009-21903 on this PUN — that API belongs to the permit-only Riviera 9H (approved 10/2/2013, expired 4/2/2014); conflict carried. Operator chain per official OCC forms: Linn → EnerVest → BP → Latigo.</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>A14:Q14</t>
+          <t>A15:Q15</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Carlson 32-11-25 12H / 35-009-21893</t>
+          <t>Carlson 32-11-25 7H / 35-009-21923</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Gas through 5/2026; 5/2026 = 2,113 MCF (OTC PUN 009-211663-0-0000, Active, 640 ac). OTC displays API 009-21903 on this PUN — that API belongs to the permit-only Riviera 9H (approved 10/2/2013, expired 4/2/2014); conflict carried. Operator chain per official OCC forms: Linn → EnerVest → BP → Latigo.</t>
+          <t>Historic completion facts only — not proof of current production, lease HBP or title.</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>A15:Q15</t>
+          <t>A16:Q16</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>Carlson 32-11-25 7H / 35-009-21923</t>
+          <t>Carlson 32-11-25 10H / 35-009-21933</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
@@ -6012,40 +6012,8 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>Well 1</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>A16:Q16</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>Carlson 32-11-25 10H / 35-009-21933</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
-        <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
-        </is>
-      </c>
-      <c r="E167" s="2" t="inlineStr">
-        <is>
-          <t>Historic completion facts only — not proof of current production, lease HBP or title.</t>
-        </is>
-      </c>
-      <c r="F167" s="2" t="inlineStr">
-        <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F167"/>
+  <autoFilter ref="A1:F166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
+++ b/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Conflict Register" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cell Lineage'!$A$1:$F$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cell Lineage'!$A$1:$F$167</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Latest supported named claimant</t>
+          <t>Latest supported named claimant through search cutoff</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Later context only</t>
+          <t>Potential post-cutoff divestiture; Section 32 effect unknown</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
@@ -5331,44 +5331,44 @@
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>2451/4-23; 2476/121</t>
+          <t>2434/751</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Read complete instruments</t>
+          <t>Read complete assignment and schedule before calling Diversified current</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>WI 2</t>
+          <t>WI 1</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A13:H13</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Historic only; survival open</t>
+          <t>Later context only</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>LC, V7, V10, FV</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>502/267</t>
+          <t>2451/4-23; 2476/121</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Payout, reversion and releases</t>
+          <t>Read complete instruments</t>
         </is>
       </c>
     </row>
@@ -5380,12 +5380,12 @@
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A5:H5</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Historic allocation only</t>
+          <t>Historic only; survival open</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>509/220</t>
+          <t>502/267</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Prove baseline and successors</t>
+          <t>Payout, reversion and releases</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A6:H6</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Historic only; status open</t>
+          <t>Historic allocation only</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>845/47</t>
+          <t>509/220</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Read unrecorded agreement and releases</t>
+          <t>Prove baseline and successors</t>
         </is>
       </c>
     </row>
@@ -5444,12 +5444,12 @@
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A7:H7</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Historic only; bridge open</t>
+          <t>Historic only; status open</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -5459,12 +5459,12 @@
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>872/279</t>
+          <t>845/47</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Complete instrument and 1984 agreement</t>
+          <t>Read unrecorded agreement and releases</t>
         </is>
       </c>
     </row>
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A8:H8</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Nemo-dat/source-title defect</t>
+          <t>Historic only; bridge open</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>1014/75</t>
+          <t>872/279</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Prove assignor WI source</t>
+          <t>Complete instrument and 1984 agreement</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>A10:H10</t>
+          <t>A9:H9</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Separate branch; do not blend</t>
+          <t>Nemo-dat/source-title defect</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2183/174; 2185/639</t>
+          <t>1014/75</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Read complete exhibits and legal</t>
+          <t>Prove assignor WI source</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>A11:H11</t>
+          <t>A10:H10</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Parallel portfolio branch</t>
+          <t>Separate branch; do not blend</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
@@ -5555,44 +5555,44 @@
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>2185/639; 2225/1; 2415/328</t>
+          <t>2183/174; 2185/639</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Reconcile Teocalli carve and schedules</t>
+          <t>Read complete exhibits and legal</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>WI 2</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>A3:Q3</t>
+          <t>A11:H11</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Cora Garrett C-310 / 35-009-00075</t>
+          <t>Parallel portfolio branch</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV, V7, V10, MT</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>2185/639; 2225/1; 2415/328</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Reconcile Teocalli carve and schedules</t>
         </is>
       </c>
     </row>
@@ -5604,12 +5604,12 @@
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>A4:Q4</t>
+          <t>A3:Q3</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Crook 1-32 / 35-009-20312</t>
+          <t>Cora Garrett C-310 / 35-009-00075</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>No rolling-12-month OTC rows (PUN 009-066620-0-0000, Active, 640 ac, still lists BP). AC/DRY under Complete Oil &amp; Gas Services LLC; Latigo-to-Complete Form 1073MW approved 12/3/2025 (Crook first of 38 wells). AC proves an open wellbore — NOT production or HBP.</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>A5:Q5</t>
+          <t>A4:Q4</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Pearl 1-32 / 35-009-20605</t>
+          <t>Crook 1-32 / 35-009-20312</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>No rolling-12-month OTC rows (PUN 009-066620-0-0000, Active, 640 ac, still lists BP). AC/DRY under Complete Oil &amp; Gas Services LLC; Latigo-to-Complete Form 1073MW approved 12/3/2025 (Crook first of 38 wells). AC proves an open wellbore — NOT production or HBP.</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>A6:Q6</t>
+          <t>A5:Q5</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Legrand 1-32 / 35-009-20738</t>
+          <t>Pearl 1-32 / 35-009-20605</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>A7:Q7</t>
+          <t>A6:Q6</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>JGL 1-32 / 35-009-21072</t>
+          <t>Legrand 1-32 / 35-009-20738</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Gas reported 7/2025-4/2026; 4/2026 = 2,367 MCF (OTC PUN 009-101800-0-0000, reported by NextEra Energy Marketing). Production fact only — HBP not concluded.</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -5732,12 +5732,12 @@
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>A8:Q8</t>
+          <t>A7:Q7</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Hanks Crook 1-32 / 35-009-21085</t>
+          <t>JGL 1-32 / 35-009-21072</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Active PUN returned no rolling-12-month rows on 7/9/2026.</t>
+          <t>Gas reported 7/2025-4/2026; 4/2026 = 2,367 MCF (OTC PUN 009-101800-0-0000, reported by NextEra Energy Marketing). Production fact only — HBP not concluded.</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>A9:Q9</t>
+          <t>A8:Q8</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Crook-Legrand 1-32 / 35-009-21166</t>
+          <t>Hanks Crook 1-32 / 35-009-21085</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>Active PUN returned no rolling-12-month rows on 7/9/2026.</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>A10:Q10</t>
+          <t>A9:Q9</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Legrand 1-32 / 35-009-21236</t>
+          <t>Crook-Legrand 1-32 / 35-009-21166</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>A11:Q11</t>
+          <t>A10:Q10</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Katie 1-32 / 35-009-21245</t>
+          <t>Legrand 1-32 / 35-009-21236</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>A12:Q12</t>
+          <t>A11:Q11</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Legrand 2-32 / 35-009-21258</t>
+          <t>Katie 1-32 / 35-009-21245</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>A13:Q13</t>
+          <t>A12:Q12</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Twin 1-32 / 35-009-21391</t>
+          <t>Legrand 2-32 / 35-009-21258</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>A14:Q14</t>
+          <t>A13:Q13</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Carlson 32-11-25 12H / 35-009-21893</t>
+          <t>Twin 1-32 / 35-009-21391</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Gas through 5/2026; 5/2026 = 2,113 MCF (OTC PUN 009-211663-0-0000, Active, 640 ac). OTC displays API 009-21903 on this PUN — that API belongs to the permit-only Riviera 9H (approved 10/2/2013, expired 4/2/2014); conflict carried. Operator chain per official OCC forms: Linn → EnerVest → BP → Latigo.</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>A15:Q15</t>
+          <t>A14:Q14</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Carlson 32-11-25 7H / 35-009-21923</t>
+          <t>Carlson 32-11-25 12H / 35-009-21893</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Historic completion facts only — not proof of current production, lease HBP or title.</t>
+          <t>Gas through 5/2026; 5/2026 = 2,113 MCF (OTC PUN 009-211663-0-0000, Active, 640 ac). OTC displays API 009-21903 on this PUN — that API belongs to the permit-only Riviera 9H (approved 10/2/2013, expired 4/2/2014); conflict carried. Operator chain per official OCC forms: Linn → EnerVest → BP → Latigo.</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
@@ -5988,32 +5988,64 @@
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
+          <t>A15:Q15</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Carlson 32-11-25 7H / 35-009-21923</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Historic completion facts only — not proof of current production, lease HBP or title.</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>A16:Q16</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C167" s="2" t="inlineStr">
         <is>
           <t>Carlson 32-11-25 10H / 35-009-21933</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>FV official OCC/OTC synthesis; V10 well register</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>Historic completion facts only — not proof of current production, lease HBP or title.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F166"/>
+  <autoFilter ref="A1:F167"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6286,7 +6318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6647,6 +6679,33 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>C-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Post-cutoff Bk 2434/Pg 751 assigns assets from Diversified/DP Legacy Central to Teocalli, but its schedule is unread.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>V10 current-WI master; post-03/02/2023 index metadata</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Diversified is described only as the latest supported named claimant through Bk 2400/Pg 551-567, subject to this potential later divestiture.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Read the complete 2434/751 assignment and determine whether Section 32 or OK48147.001.1 is included.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
+++ b/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
@@ -755,7 +755,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 65.000000 NMA residual vests in last traced record owner (WD 10/255); no chain-out located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: WD 10/255. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: 65.000000 NMA residual vests in last traced record owner (WD 10/255); no chain-out located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: WD 10/255. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 92/47; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 92/47. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 92/47; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 92/47. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 367/632; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 367/632. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 367/632; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 367/632. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 250/26; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 250/26. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 250/26; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 250/26. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 845/150-152 and 845/157; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 845/150-152 and 845/157. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 40.000000 NMA vests collectively per decree; individual allocations not stated on the face. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: 40.000000 NMA vests collectively per decree; individual allocations not stated on the face. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: holds 1.500000 NMA per the recorded deed; grantee name not extracted from the face. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: holds 1.500000 NMA per the recorded deed; grantee name not extracted from the face. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/365 corr. 87/174; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/365 corr. 87/174. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/365 corr. 87/174; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/365 corr. 87/174. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 312/700-704. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 312/700-704. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/424; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/424. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/424; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/424. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/363; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/363. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/363; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/363. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/245; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/245. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/245; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/245. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/428; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/428. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/428; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/428. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/426; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/426. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/426; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/426. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/364; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/364. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/364; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/364. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/366; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/366. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/366; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/366. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1555,7 +1555,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 88/172; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/172. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 88/172; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/172. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/87; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/87. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/87; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/87. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/422; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/422. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/422; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/422. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 12.166667 NMA carried in the Farrar fee chain; connecting instrument not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: 12.166667 NMA carried in the Farrar fee chain; connecting instrument not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 6.750000 NMA per 92/468 (index) and later family instruments not read. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: 92/468. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: 6.750000 NMA per 92/468 (index) and later family instruments not read. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: 92/468. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 86/21; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 86/21. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 86/21; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 86/21. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 13.333333 NMA residue exposed by DECR P-76-78 vests in untraced Keathley successors. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: 13.333333 NMA residue exposed by DECR P-76-78 vests in untraced Keathley successors. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/36; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/36. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/36; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/36. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR P-76-78, pages 349-350 (images 1546-1550). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR P-76-78, pages 349-350 (images 1546-1550). Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR P-76-78, pages 349-350 (images 1546-1550). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR P-76-78, pages 349-350 (images 1546-1550). Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 74/63; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 74/63. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 74/63; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 74/63. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR P-76-78, pages 349-350 (images 1546-1550). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR P-76-78, pages 349-350 (images 1546-1550); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR P-76-78, pages 349-350 (images 1546-1550). Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: STIPULATION (RECORDED QUANTUM) 153/161-162; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: STIPULATION (RECORDED QUANTUM) 153/161-162. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 312/700-704. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 312/700-704. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/424; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/424. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/424; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/424. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 333/239-248; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 333/239-248. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 333/239-248; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 333/239-248. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -2163,7 +2163,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 88/174; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/174. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 88/174; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/174. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1287/42; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1287/42. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/428; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/428. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/428; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/428. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/426; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/426. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/426; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/426. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 90/242; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 90/242. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 90/242; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 90/242. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 88/172; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/172. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 88/172; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/172. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 90/241; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 90/241. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 90/241; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 90/241. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/87; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/87. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/87; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/87. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/422; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/422. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/422; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/422. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 90/153; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 90/153. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 90/153; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 90/153. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/315; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/315. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/315; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/315. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/222; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/222. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/222; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/222. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 262/490-493 (P-71-473); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 262/490-493 (P-71-473). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 262/490-493 (P-71-473); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 262/490-493 (P-71-473). Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 14.166667 NMA carried in the Stevens chain; connecting instrument not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: 14.166667 NMA carried in the Stevens chain; connecting instrument not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 81/194; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 81/194. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 81/194; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 81/194. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 35.000000 NMA carried in the Stevens chain; connecting instrument not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: 35.000000 NMA carried in the Stevens chain; connecting instrument not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 92/115 (previously mis-cited 92/120); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 92/115 (previously mis-cited 92/120). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 92/115 (previously mis-cited 92/120); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 92/115 (previously mis-cited 92/120). Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1063/166; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1063/166. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1063/166; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1063/166. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 27.674000 NMA residual vests in OGL 1 lessors of record; succession untraced. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: 27.674000 NMA residual vests in OGL 1 lessors of record; succession untraced. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/365 corr. 87/174; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/365 corr. 87/174. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/365 corr. 87/174; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/365 corr. 87/174. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 312/700-704. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 312/700-704; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 312/700-704. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/424; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/424. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/424; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/424. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/363; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/363. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/363; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/363. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/244; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/244. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/244; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/244. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/428; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/428. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/428; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/428. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/426; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/426. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/426; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/426. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1090/94; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1090/94. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1090/94; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1090/94. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/364; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/364. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/364; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/364. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 85/366; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/366. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 85/366; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 85/366. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 88/172; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/172. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 88/172; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 88/172. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1063/164; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1063/164. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1063/164; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1063/164. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1423/148; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1423/148. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1423/148; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1423/148. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: ORDER 311/817-828; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: ORDER 311/817-828. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/87; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/87. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/87; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/87. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1063/164; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1063/164. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1063/164; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1063/164. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 89/422; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/422. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 89/422; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 89/422. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 1090/95 (face stamp; index reads 96); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1090/95 (face stamp. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 1090/95 (face stamp; index reads 96); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 1090/95 (face stamp. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: DECR 262/490-493 (P-71-473); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 262/490-493 (P-71-473). Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: DECR 262/490-493 (P-71-473); EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: DECR 262/490-493 (P-71-473). Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 81/194; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 81/194. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 81/194; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 81/194. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>ASSUMED: 35.000000 NMA residual vests in last record owner; Garrett chain-out not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>ASSUMED: 35.000000 NMA residual vests in last record owner; Garrett chain-out not located. V10 STATUS: UNRESOLVED — NOT A PROVED CURRENT OWNER. Vesting/source reference: Not stated on Title row. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>EST. last located record owner; Vested: MD 92/115; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 92/115. Forward record search stops 03/02/2023; current status at 08/06/2026 is not confirmed.</t>
+          <t>EST. last located record owner; Vested: MD 92/115; EST.* V10 STATUS: LATEST LOCATED RECORD OWNER — CURRENT STATUS NOT PROVED. Vesting/source reference: MD 92/115. Complete corpus/face review stops 03/02/2023; later Drive/OCR index-only evidence through Bk 2490/Pg 471 does not confirm current status at 08/06/2026.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">

--- a/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
+++ b/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Source Inventory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cell Lineage" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Component Selection" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Conflict Register" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source Inventory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cell Lineage" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Component Selection" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conflict Register" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cell Lineage'!$A$1:$F$166</definedName>
@@ -6024,13 +6024,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6041,15 +6042,20 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Winning Candidate</t>
+          <t>Contestant Supplier</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Winning Candidate Inputs</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Why Selected</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Merged Additions</t>
         </is>
@@ -6063,15 +6069,20 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>FV + V10</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>FV has template parity and strongest controlling qualification</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Effective date, estimated-owner method and cure list from V10</t>
         </is>
@@ -6085,15 +6096,20 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>V7 geometry rebuilt in FV style</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Seven fee tracts cover the section and are readable at one-page scale</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Leasehold-overlay warning from MT/LC</t>
         </is>
@@ -6107,15 +6123,20 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>V7 + V10</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>V7 has most complete owners/NMA/addresses; V10 identifies present-vesting defects</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>All HBP and current-owner labels qualified</t>
         </is>
@@ -6129,15 +6150,20 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>MT + V7 + FV</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>MT reviewed 11 original faces; V7 adds Viersen; FV/LC adds Minton/Hartman</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Uniform lease-specific status qualifications</t>
         </is>
@@ -6151,15 +6177,20 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>FV</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Most complete verified chronology</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Missing 1016 series and 1697/236 leads from V7/V10</t>
         </is>
@@ -6173,15 +6204,20 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>V7 + MT + FV</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Best fee/mineral ending schedules and direct-face chain facts</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Grouped by quarter to preserve 13-tab template</t>
         </is>
@@ -6195,15 +6231,20 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>LC + FV</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Strongest OK48147.001.1 modern chain</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Later corporate filings and missing bridge disclosed</t>
         </is>
@@ -6217,15 +6258,20 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>LC + V7/V10</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Strongest Diversified branch sequence and transaction split</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>51.25% expressly not treated as current WI</t>
         </is>
@@ -6239,15 +6285,20 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>FV + MT/V7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Best depth/wellbore burden detail</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Parallel Linn/FourPoint/MNR branches separated</t>
         </is>
@@ -6261,15 +6312,20 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>GPT-5-6-SOL</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>FV</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Strongest official OCC/OTC reconciliation</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>V10 conflict and HBP limitation retained</t>
         </is>

--- a/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
+++ b/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
@@ -4201,7 +4201,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>WD Roger Mills 11/214 — NE/4 fee; no reservation apparent</t>
+          <t>WD Roger Mills Co. 11/214 (pre-Beckham record) — Section 32 NE/4 fee; no reservation apparent</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">

--- a/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
+++ b/SECTION32_BEST_OF_BEST_TOURNAMENT_20260806/GPT-5-6-SOL/Section_32-11N-25W_Beckham_Co_Diversified_Cursory_Report_GPT-5-6-SOL_TOURNAMENT_20260806_SOURCE_LINEAGE.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conflict Register" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cell Lineage'!$A$1:$F$166</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cell Lineage'!$A$1:$F$275</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>V7</t>
+          <t>V7/V10</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Status not determined; HBP not independently confirmed</t>
+          <t>Status not determined; HBP not independently confirmed; owner-coverage gap</t>
         </is>
       </c>
     </row>
@@ -3908,27 +3908,27 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>A104:K104</t>
+          <t>A2:K2</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/7</t>
+          <t>Retained Section 32 runsheet entry Patent Bk 3/469</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>1016 series; index lead, face not held</t>
+          <t>Patent Bk 3/469</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Locator/qualified evidence; full instrument required</t>
+          <t>Homestead patent; no mineral reservation apparent on reviewed image.</t>
         </is>
       </c>
     </row>
@@ -3940,27 +3940,27 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>A105:K105</t>
+          <t>A3:K3</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/13</t>
+          <t>Retained Section 32 runsheet entry Image 0004</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>1016 series; index lead, face not held</t>
+          <t>Image 0004</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Locator/qualified evidence; full instrument required</t>
+          <t>Earliest supplied land-office evidence; actual patent remains OPEN.</t>
         </is>
       </c>
     </row>
@@ -3972,27 +3972,27 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>A106:K106</t>
+          <t>A4:K4</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/18</t>
+          <t>Retained Section 32 runsheet entry Image 0005</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>1016 series; index lead, face not held</t>
+          <t>Image 0005</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Locator/qualified evidence; full instrument required</t>
+          <t>Final Receiver Receipt No. 3894; actual patent remains OPEN.</t>
         </is>
       </c>
     </row>
@@ -4004,27 +4004,27 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>A107:K107</t>
+          <t>A5:K5</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/25</t>
+          <t>Retained Section 32 runsheet entry Image 0006</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>1016 series; index lead, face not held</t>
+          <t>Image 0006</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Locator/qualified evidence; full instrument required</t>
+          <t>Final Receiver Receipt No. 3895; actual patent remains OPEN.</t>
         </is>
       </c>
     </row>
@@ -4036,27 +4036,27 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>A108:K108</t>
+          <t>A6:K6</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/29</t>
+          <t>Retained Section 32 runsheet entry 376/287</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>1016 series; index lead, face not held</t>
+          <t>376/287</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Locator/qualified evidence; full instrument required</t>
+          <t>All right, title and interest; assignor reserves ORRI printed “.0125% of 8/8s” (literal decimal 0.000125 — do not normalize), free of development/operating costs except taxes. Underlying lease 341/538 dated 1977-11-29. No release found.</t>
         </is>
       </c>
     </row>
@@ -4068,27 +4068,27 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>A109:K109</t>
+          <t>A7:K7</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/33</t>
+          <t>Retained Section 32 runsheet entry OCC Order 156126; Cause CD 59995</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>1016 series; index lead, face not held</t>
+          <t>OCC Order 156126; Cause CD 59995</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Locator/qualified evidence; full instrument required</t>
+          <t>Leede Exploration pooling for proposed Sec. 32 well. $400/ac bonus or 1/16-of-8/8 elections; 20/27/35-day mechanics; 180-day commencement. Later schedules recite 8/8/1979 — conflict carried; official order date controls. Owner elections/defaults and JOA No. 1580 remain OPEN.</t>
         </is>
       </c>
     </row>
@@ -4100,27 +4100,27 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>A110:K110</t>
+          <t>A8:K8</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1016/90</t>
+          <t>Retained Section 32 runsheet entry 407/676-683</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>1016 series; index lead, face not held</t>
+          <t>407/676-683</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Locator/qualified evidence; full instrument required</t>
+          <t>Transfers 99% of Hunt Energy's lease interest; as-is/no warranty. Schedule prints 1/14/1978 lease date, conflicting with 11/29/1977 recited elsewhere — discrepancy carried, not harmonized.</t>
         </is>
       </c>
     </row>
@@ -4132,1888 +4132,5376 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>A111:K111</t>
+          <t>A9:K9</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Added missing Section 32 chain lead 1697/236</t>
+          <t>Retained Section 32 runsheet entry 430/416-429</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>V7, V10</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Recorded-face lead; required bridge into modern chain</t>
+          <t>430/416-429</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Locator/qualified evidence; full instrument required</t>
+          <t>Undivided 25% of each assignor's then-owned scheduled lease interest; as-is/no warranty; conditional 50% production/sale-proceeds recovery reservation — NOT a clean absolute 25% WI.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Tract 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A10:K10</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>PAT Patent 3/469 — Sovereign inception; no mineral reservation apparent</t>
+          <t>Retained Section 32 runsheet entry 423/238-335</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>P-001 / Img 0003</t>
+          <t>423/238-335</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>One GAEC mortgage ($2,750,000 note) + four GAE-III tranche mortgages (stated 73.9874%, 13.3531%, 8.6709%, 3.9886%). No release found in supplied set — carried as historic lien requirement, not a current-lien conclusion.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Tract 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A11:K11</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>WD Roger Mills Co. 11/214 (pre-Beckham record) — Section 32 NE/4 fee; no reservation apparent</t>
+          <t>Retained Section 32 runsheet entry 431/674-680</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>V7 direct-face register</t>
+          <t>431/674-680</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>All GAEC interest from prior assignment; assignor reserves formula ORRI = 25% of 8/8 less lessor royalty and other burdens, proportionately reduced; as-is/no warranty. No release found.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Tract 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A12:K12</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>WD 10/255 — Fee to Adolf; downstream chain incomplete</t>
+          <t>Retained Section 32 runsheet entry 440/269-282</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>V7 direct-face register</t>
+          <t>440/269-282</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Duplicate/re-record of 430/416-429 — corroboration only; MUST NOT be counted as a second 25% transfer.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Tract 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A13:K13</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>DECR 83/259 — Collective mineral vesting; allocations require decree</t>
+          <t>Retained Section 32 runsheet entry 470/29-68</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>V7 probate extraction</t>
+          <t>470/29-68</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Amend and continue the five 423/238-335 mortgage tranches. Amendments, not releases. Bk 425M/Pgs 672-680 amendments referenced but absent from supplied set — OPEN pull.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Tract 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A14:K14</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>DECR 845/150-157 — Five 8-NMA estimated last-located interests</t>
+          <t>Retained Section 32 runsheet entry Bk 502/P267 (supersedes Bk 471/P330)</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>V7 probate extraction</t>
+          <t>Bk 502/P267 (supersedes Bk 471/P330)</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>High quantum / current status open</t>
+          <t>Union retained 7/64 gas/condensate/distillate ORRI and 1/16 oil/casinghead-gas ORRI; no warranty; subject to unrecorded 1979 agreement. Images 1940-1943.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Tract 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>A10:H10</t>
+          <t>A15:K15</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>MD 92/47 — 1.5 NMA each per deed; later one grantee unextracted</t>
+          <t>Retained Section 32 runsheet entry 518/5-44</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>V7 direct-face register</t>
+          <t>518/5-44</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Adds DAE-II Partnership as co-mortgagor for its 15.7533% assumed share. Amendments, not releases.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Tract 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>A11:H11</t>
+          <t>A16:K16</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>MD 367/632 — 10 NMA; competing 267/638 out-conveyance must be resolved</t>
+          <t>Retained Section 32 runsheet entry Bk 509/P220 (supersedes Bk 471/P337)</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>V7 direct-face register</t>
+          <t>Bk 509/P220 (supersedes Bk 471/P337)</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Percentages total 100%. Leede reserved ORRI sufficient for 75% aggregate NRI plus 1/4 after-payout reversion; special warranty only; unrecorded Payfield agreement. Images 1949-1952.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Tract 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A17:K17</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>FR Final Receiver Receipt 3894 — Earliest located NW/4 evidence; patent not located</t>
+          <t>Retained Section 32 runsheet entry Bk 509/P176</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>P-003 / Img 0005</t>
+          <t>Bk 509/P176</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>90% identity / 0% patent</t>
+          <t>Aggregate 2.25% ORRI; cost-free except taxes; pooling/free-fuel provisions; special warranty. Images 1946-1948.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Tract 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A18:K18</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>STIP 153/161-162 — Recorded residual quantum used for estimated ending schedule</t>
+          <t>Retained Section 32 runsheet entry Bk 502/P265</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>V7 title register</t>
+          <t>Bk 502/P265</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Medium-high</t>
+          <t>Allocations total 100.000%; expressly excludes Leede's after-payout Crook WI. Images 1938-1939.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Tract 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A19:K19</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>MD/ORDER 85/363-366; 311/817-828 — Estimated last-located mineral interests</t>
+          <t>Retained Section 32 runsheet entry 546/68-74</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>V7 title register</t>
+          <t>546/68-74</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>Varies; current status open</t>
+          <t>Undivided 15.7533% of the interest GAEC conveyed to GAE-III — a fraction of a prior fraction, NOT 15.7533% of 8/8; subject to proportional burdens; no warranty.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Tract 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A20:K20</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>DECR P-76-78 — Decree allocation incomplete; 13.333333-NMA residual assumed</t>
+          <t>Retained Section 32 runsheet entry 568/121-191</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>V7 title register</t>
+          <t>568/121-191</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Consolidation, two restatements, and Third Amendment (GAEC note changed to $2,350,000 demand, eff. 2/26/1982). None is a release — lien family carried as requirement.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Tract 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A21:K21</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>OGL 340/323 — N/2 NW/4 plus N/2 SW/4; no current HBP conclusion</t>
+          <t>Retained Section 32 runsheet entry 568/26-34</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Direct face</t>
+          <t>568/26-34</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>High terms / open status</t>
+          <t>All Trust right, title and interest — the stated 2% Hunt-allocation branch, subject to the earlier 25%-of-branch GAEC transfer and existing burdens.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Tract 3</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A22:K22</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>FR Final Receiver Receipt 3895 — Earliest located SW/4 evidence; patent not located</t>
+          <t>Retained Section 32 runsheet entry 678/777-811</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>P-004 / Img 0006</t>
+          <t>678/777-811</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>90% identity / 0% patent</t>
+          <t>Conveys 58% of Hunt Petroleum's then-owned interest (42% retained). Schedule states assignor-row NRI .0999600000 / WI .1230500000 — schedule-stated figures, second visual check required before ANY use in math.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Tract 3</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A23:K23</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>MD 81/194 — 40 NMA in S/2 SW/4 ending schedule</t>
+          <t>Retained Section 32 runsheet entry 792/51-58</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>V7 title register</t>
+          <t>792/51-58</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
-          <t>Medium; current status open</t>
+          <t>Releases Bk 611/154 only as to scheduled ENI Crook-unit properties. Schedule does not list the Minton-Hartman lease, so this release does NOT reach the Hartman or Great American burdens.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Tract 3</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A24:K24</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>MD/DECR 85/222; 262/490-493 — Estimated last-located interests</t>
+          <t>Retained Section 32 runsheet entry 792/72-101</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>V7 title register</t>
+          <t>792/72-101</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
-          <t>Varies</t>
+          <t>5% scheduled leasehold/pooled-rights interest + stated 4.0144 Garrett-lease interest; exhibit states before-payout OI .0495703/NRI .0371778, after-payout OI .0371778/NRI .0278833. Distinct Crook-unit chain; three vintage ENI “Diversified Drilling Program” names are a name collision — NO bridge to modern Diversified.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Tract 3</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A25:K25</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>OGL 340/302; 340/304; 342/564; 342/566 — Overlapping N/2 SW/4 leases; not additive</t>
+          <t>Retained Section 32 runsheet entry Bk 839/P188</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>Direct faces</t>
+          <t>Bk 839/P188</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
-          <t>High terms / open status</t>
+          <t>No warranty. Does not identify or transfer the Bank's separate 1% Crook participant WI. Images 4103.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Tract 3</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A26:K26</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>ASG 872/279 — Top Morrow-19,480 ft; ORRIs reserved; modern bridge open</t>
+          <t>Retained Section 32 runsheet entry Bk 845/P47</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>Direct images</t>
+          <t>Bk 845/P47</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
-          <t>98% historic / open current</t>
+          <t>Reserves 1/8 of 8/8 ORRI; five-year renewal/extension reach; subject to unrecorded 1985 agreement; no warranty. Images 4120-4121.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Tract 4</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A27:K27</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>FR Final Receiver Receipt — Earliest located SE/4 evidence; Biggs/Bigge patent remains missing</t>
+          <t>Retained Section 32 runsheet entry Bk 872/P279</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>P-002 / Img 0004</t>
+          <t>Bk 872/P279</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>90% identity / 0% patent</t>
+          <t>Reserves 1/8 gas/condensate/distillate ORRI and 1/16 oil/casinghead-gas ORRI; no warranty; unrecorded 1984 agreement. Images 4386-4393.</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Tract 4</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A28:K28</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>OGL 63/33 — E/2 SE/4, 1/8 royalty, 10-year term; present status open</t>
+          <t>Retained Section 32 runsheet entry Bk 903/P50</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Direct face</t>
+          <t>Bk 903/P50</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>98% terms</t>
+          <t>Before package payout: each PRF .526300% and Leede 98.421100% of LGWI; after payout: each PRF 1.315750% and Leede 96.052750%. Percentages apply to defined LGWI, not 8/8 WI. Images 4438-4463.</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Tract 4</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A29:K29</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>ASG 244/432 — Historic 63/33 assignment branch</t>
+          <t>Retained Section 32 runsheet entry Bk 987/P159 et seq.</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Direct image</t>
+          <t>Bk 987/P159 et seq.</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>Reserves ORRI equal to .5% of Leede NRI: McCall .043146%, Pearl .052310%, Crook 0%; no title warranty. Images 4840-4857.</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Tract 4</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A30:K30</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>WB ASG 845/47 — Pearl wellbore 11,100-19,480 ft; 1/8 ORRI</t>
+          <t>Retained Section 32 runsheet entry Bk 995/P52</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Direct image</t>
+          <t>Bk 995/P52</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
-          <t>98% historic</t>
+          <t>Full/final release of enumerated 1984/1987 TCW, Vinson and First City liens; does not prove release of any unlisted lien. Images 4868-4870.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Tract 4</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A31:K31</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>OGL 307/31 — W/2 SE/4 and S/2 SW/4; present status open</t>
+          <t>Retained Section 32 runsheet entry Bk 1014/P75</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Direct face</t>
+          <t>Bk 1014/P75</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>98% terms</t>
+          <t>Purports to assign all OGLs and working/cost-bearing interests without warranty. Source into Consolidation proves only royalty/ORRI; no WI source or decimal shown. Does not expressly reconvey the 52.632% royalty/ORRI strand. Images 4893.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Tract 5</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A32:K32</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>ASG 1697/236 — Scheduled predecessor lead; full Exhibit A controls</t>
+          <t>Retained Section 32 runsheet entry 1014/76</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Recorded face / Exhibit A required</t>
+          <t>1014/76</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>First post-cutoff assignment; complete copy and schedule required.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Tract 5</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A33:K33</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>ASG 2340/490 — Full-section indexed; missing Tapstone/asset bridge schedules</t>
+          <t>Retained Section 32 runsheet entry 1014/228</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Index / schedule missing</t>
+          <t>1014/228</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>High metadata / low scope</t>
+          <t>Post-cutoff assignment; complete copy and schedule required.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Tract 5</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A34:K34</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>ASG 2371/470-494 — 51.25%/48.75% transaction branches; not current WI</t>
+          <t>Retained Section 32 runsheet entry 1016/38</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Index / instrument partial</t>
+          <t>1016/38</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
-          <t>High parties / low asset quantum</t>
+          <t>Early post-cutoff transfer; underlying copy absent</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Tract 5</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A35:K35</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>MERGER 2389/500-580 — Corporate consolidation; asset-specific effect open</t>
+          <t>Retained Section 32 runsheet entry 1137/65</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Index / certificate missing</t>
+          <t>1137/65</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>High metadata</t>
+          <t>Possible royalty/ORRI burden</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Tract 5</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A36:K36</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>CONV 2395/415-464 — OK48147.001.1 identified; allocation/estate/depth blank</t>
+          <t>Retained Section 32 runsheet entry 1137/340; 1140/1</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Reviewed asset line 2395/462</t>
+          <t>1137/340; 1140/1</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
-          <t>High asset identity / low quantum</t>
+          <t>Potential title clarification</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Tract 5</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>A10:H10</t>
+          <t>A37:K37</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>CONV 2400/551-567 — Latest supported named claimant; exact current WI/NRI open</t>
+          <t>Retained Section 32 runsheet entry 1217/304; 1217/318</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Reviewed asset line 2400/566</t>
+          <t>1217/304; 1217/318</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>High asset identity / low quantum</t>
+          <t>Possible outstanding leasehold slices</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Tract 5</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>A11:H11</t>
+          <t>A38:K38</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>AGMT 2476/121-130 — Agreement, not facial conveyance; current vesting effect open</t>
+          <t>Retained Section 32 runsheet entry 1257/197</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Index/public metadata</t>
+          <t>1257/197</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>High metadata / low title effect</t>
+          <t>Potential full-section royalty/ORRI conveyance</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>WI 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A39:K39</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Historic scheduled predecessor lead</t>
+          <t>Retained Section 32 runsheet entry 1303/202</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>LC, V7, V10, FV</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>1697/236</t>
+          <t>1303/202</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>Full Exhibit A required</t>
+          <t>Full-section-indexed Exxon link</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>WI 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A40:K40</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Potential bridge branch</t>
+          <t>Retained Section 32 runsheet entry 1346/34; 1442/270</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>LC, V7, V10, FV</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>2340/403</t>
+          <t>1346/34; 1442/270</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
-          <t>Missing Tapstone schedule/bridge</t>
+          <t>Leede operating branch</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>WI 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A41:K41</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Principal indexed predecessor</t>
+          <t>Retained Section 32 runsheet entry 1522/84; 1522/87</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>LC, V7, V10, FV</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>2340/490</t>
+          <t>1522/84; 1522/87</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Asset schedule absent</t>
+          <t>Potential outstanding/divested branch</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>WI 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A42:K42</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Keep branches separate</t>
+          <t>Retained Section 32 runsheet entry 1524/36; 1533/362</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>LC, V7, V10, FV</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>2371/470-494</t>
+          <t>1524/36; 1533/362</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>Not current Section 32 WI</t>
+          <t>Separate/partial branches; exact tracts open</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>WI 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A43:K43</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Merger path</t>
+          <t>Retained Section 32 runsheet entry 1577/450; 1581/303; 1581/319</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>LC, V7, V10, FV</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>2389/500-580</t>
+          <t>1577/450; 1581/303; 1581/319</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Certificate and schedules absent</t>
+          <t>Potential outstanding branch/title clarification</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>WI 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>A10:H10</t>
+          <t>A44:K44</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Asset identity supported</t>
+          <t>Retained Section 32 runsheet entry 1697/574</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>LC, V7, V10, FV</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>2395/415-464</t>
+          <t>1697/574</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Estate/depth/quantum blank</t>
+          <t>Full-section-indexed Chesapeake acquisition</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>WI 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>A11:H11</t>
+          <t>A45:K45</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Latest supported named claimant</t>
+          <t>Retained Section 32 runsheet entry 1783/118; 1784/959</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>LC, V7, V10, FV</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>2400/551-567</t>
+          <t>1783/118; 1784/959</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Later filings and exact quantum open</t>
+          <t>Partial-tract predecessor links</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>WI 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>A12:H12</t>
+          <t>A46:K46</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Later context only</t>
+          <t>Retained Section 32 runsheet entry 2042/183-197</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>LC, V7, V10, FV</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>2451/4-23; 2476/121</t>
+          <t>2042/183-197</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Read complete instruments</t>
+          <t>Index-gap fill (missing logical p.48): surface/wind-energy context; operative terms require image.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>WI 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>A5:H5</t>
+          <t>A47:K47</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Historic only; survival open</t>
+          <t>Retained Section 32 runsheet entry 2043/917-919</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>502/267</t>
+          <t>2043/917-919</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>Payout, reversion and releases</t>
+          <t>Index-gap fill; party orientation per public row — verify scan if orientation matters.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>WI 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>A6:H6</t>
+          <t>A48:K48</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>Historic allocation only</t>
+          <t>Retained Section 32 runsheet entry 2052/466-469</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>509/220</t>
+          <t>2052/466-469</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>Prove baseline and successors</t>
+          <t>Index-gap fill; deed estate/legal require image.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>WI 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>A7:H7</t>
+          <t>A49:K49</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>Historic only; status open</t>
+          <t>Retained Section 32 runsheet entry 2052/476-478; 2052/479-481</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>845/47</t>
+          <t>2052/476-478; 2052/479-481</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>Read unrecorded agreement and releases</t>
+          <t>Index-gap fill; terminated instruments/scope require images.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>WI 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>A8:H8</t>
+          <t>A50:K50</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Historic only; bridge open</t>
+          <t>Retained Section 32 runsheet entry 2077/190-196; 2077/197-201</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>872/279</t>
+          <t>2077/190-196; 2077/197-201</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>Complete instrument and 1984 agreement</t>
+          <t>Index-gap fill; operative easement terms require images. Long Description records in the 2/12/2011-2/8/2012 bracket remain OPEN.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>WI 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>A9:H9</t>
+          <t>A51:K51</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Nemo-dat/source-title defect</t>
+          <t>Retained Section 32 runsheet entry 2167/241</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>1014/75</t>
+          <t>2167/241</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>Prove assignor WI source</t>
+          <t>Input to FourPoint branch; schedule required.</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>WI 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>A10:H10</t>
+          <t>A52:K52</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Separate branch; do not blend</t>
+          <t>Retained Section 32 runsheet entry 2168/44</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>2183/174; 2185/639</t>
+          <t>2168/44</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>Read complete exhibits and legal</t>
+          <t>Additional FourPoint input; some transcriptions show a page discrepancy — record controls.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>WI 2</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>A11:H11</t>
+          <t>A53:K53</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Parallel portfolio branch</t>
+          <t>Retained Section 32 runsheet entry 2183/174</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>FV, V7, V10, MT</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>2185/639; 2225/1; 2415/328</t>
+          <t>2183/174</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>Reconcile Teocalli carve and schedules</t>
+          <t>Potential wellbore-specific divestiture</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>A3:Q3</t>
+          <t>A54:K54</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Cora Garrett C-310 / 35-009-00075</t>
+          <t>Retained Section 32 runsheet entry 2185/639; 2225/1; 2225/710</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>2185/639; 2225/1; 2225/710</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>FourPoint branch; wellbore/depth/excluded assets open</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>A4:Q4</t>
+          <t>A55:K55</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Crook 1-32 / 35-009-20312</t>
+          <t>Retained Section 32 runsheet entry 2327/1</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>No rolling-12-month OTC rows (PUN 009-066620-0-0000, Active, 640 ac, still lists BP). AC/DRY under Complete Oil &amp; Gas Services LLC; Latigo-to-Complete Form 1073MW approved 12/3/2025 (Crook first of 38 wells). AC proves an open wellbore — NOT production or HBP.</t>
+          <t>2327/1</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>CRITICAL: county shows BP→Ellipse BEFORE OCC's 5/14/2020 BP-to-Latigo operator transfer; no county-title bridge to Latigo or Diversified is proved.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>A5:Q5</t>
+          <t>A56:K56</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Pearl 1-32 / 35-009-20605</t>
+          <t>Retained Section 32 runsheet entry 2327/108</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>2327/108</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Companion to 2327/1; exact type, parties and schedule require image.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>A6:Q6</t>
+          <t>A57:K57</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Legrand 1-32 / 35-009-20738</t>
+          <t>Retained Section 32 runsheet entry 2328/269</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>2328/269</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Latigo collateral mortgage in current Carlson producer chain; no full release located — potentially outstanding.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>A7:Q7</t>
+          <t>A58:K58</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>JGL 1-32 / 35-009-21072</t>
+          <t>Retained Section 32 runsheet entry 2328/379</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Gas reported 7/2025-4/2026; 4/2026 = 2,367 MCF (OTC PUN 009-101800-0-0000, reported by NextEra Energy Marketing). Production fact only — HBP not concluded.</t>
+          <t>2328/379</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Companion financing statement to 2328/269.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>A8:Q8</t>
+          <t>A59:K59</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Hanks Crook 1-32 / 35-009-21085</t>
+          <t>Retained Section 32 runsheet entry 2340/218</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Active PUN returned no rolling-12-month rows on 7/9/2026.</t>
+          <t>2340/218</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>FourPoint/Unbridled identity evidence</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>A9:Q9</t>
+          <t>A60:K60</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Crook-Legrand 1-32 / 35-009-21166</t>
+          <t>Retained Section 32 runsheet entry 2340/403</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>2340/403</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Full-section-indexed Tapstone branch</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>A10:Q10</t>
+          <t>A61:K61</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Legrand 1-32 / 35-009-21236</t>
+          <t>Retained Section 32 runsheet entry 2340/490</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>2340/490</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Full-section-indexed KL CHK branch</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>A11:Q11</t>
+          <t>A62:K62</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Katie 1-32 / 35-009-21245</t>
+          <t>Retained Section 32 runsheet entry 2365/743</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>2365/743</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Amends the 2020 Latigo mortgage family; no full release located.</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>A12:Q12</t>
+          <t>A63:K63</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Legrand 2-32 / 35-009-21258</t>
+          <t>Retained Section 32 runsheet entry 2371/439</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>2371/439</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Releases the Bk 2341/127 mortgage family; confirm complete released collateral.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>A13:Q13</t>
+          <t>A64:K64</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Twin 1-32 / 35-009-21391</t>
+          <t>Retained Section 32 runsheet entry 2371/470-494; I-2022-000152</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>2371/470-494; I-2022-000152</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Long description; all Section 32 Q-Q boxes indexed; fractions/schedules absent</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>A14:Q14</t>
+          <t>A65:K65</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Carlson 32-11-25 12H / 35-009-21893</t>
+          <t>Retained Section 32 runsheet entry 2371/495; 2371/514</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
         <is>
-          <t>Gas through 5/2026; 5/2026 = 2,113 MCF (OTC PUN 009-211663-0-0000, Active, 640 ac). OTC displays API 009-21903 on this PUN — that API belongs to the permit-only Riviera 9H (approved 10/2/2013, expired 4/2/2014); conflict carried. Operator chain per official OCC forms: Linn → EnerVest → BP → Latigo.</t>
+          <t>2371/495; 2371/514</t>
         </is>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Parallel co-acquirer branch; operative terms absent</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Well 1</t>
+          <t>Runsheet</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>A15:Q15</t>
+          <t>A66:K66</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>Carlson 32-11-25 7H / 35-009-21923</t>
+          <t>Retained Section 32 runsheet entry 2371/533</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>FV official OCC/OTC synthesis; V10 well register</t>
+          <t>FV</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
         <is>
-          <t>Historic completion facts only — not proof of current production, lease HBP or title.</t>
+          <t>2371/533</t>
         </is>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+          <t>Notice of relationship; not independently dispositive</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>A67:K67</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2377/635</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>2377/635</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Partially releases 2328/269 and 2365/743 family; partial release does not establish full satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>A68:K68</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2389/500-580; I-2022-003506</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>2389/500-580; I-2022-003506</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Corporate succession entry across Section 32; certificate/terms absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>A69:K69</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2389/581</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>2389/581</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Corporate identity notice; not a conveyance</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>A70:K70</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2395/370</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>2395/370</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Release in direct branch; confirm referenced mortgage and collateral.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>A71:K71</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2395/415-464; I-2022-004838</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>2395/415-464; I-2022-004838</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Long description; all Section 32 Q-Q boxes indexed; estates/fractions/schedules absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>A72:K72</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2395/973</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>2395/973</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Companion termination to 2395/967-972; confirm referenced filing. Not a title conveyance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>A73:K73</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2400/551-567; I-2023-000796</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>2400/551-567; I-2023-000796</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Long description; relation to prior branch and subject asset fraction open</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>A74:K74</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2401/214</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>2401/214</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL potential carveout ahead of the Maverick/Diversified sequence — exact leases, wells, depths, reservations and retained interests unknown until the schedule is read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>A75:K75</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2415/1</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>2415/1</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>New Latigo mortgage; no final release located through the 5/12/2026 tract cutoff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>A76:K76</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2415/328</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>2415/328</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>Later FourPoint/Unbridled securitization branch; reconcile to Tapstone/KL CHK</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>A77:K77</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2415/410</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>2415/410</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>MNR ABS collateral lien; NO release found in current search — apparently outstanding; verify. The 2025 JPMorgan releases do NOT reach this family.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>A78:K78</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2415/515</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>2415/515</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>Companion financing/collateral instrument; exact party list and collateral schedule require image.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>A79:K79</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2415/617</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>2415/617</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Related MNR ABS agreement; operative relationship requires full text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>A80:K80</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2451/4-23; I-2025-001808</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>2451/4-23; I-2025-001808</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Corporate merger metadata; merged/surviving entities and title effect absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>A81:K81</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2470/153</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>2470/153</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Amended mortgage in current producer chain; relationship to the prior Lone Star lien requires full text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>A82:K82</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2474/292</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>2474/292</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Partial release in the Latigo lien family; no final/full release located through the 5/12/2026 tract cutoff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>A83:K83</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2476/1</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>2476/1</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Separate DP-affiliated acquisition; relation to subject Diversified branch open</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>A84:K84</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2476/121-130; I-2026-000215</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>2476/121-130; I-2026-000215</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>Agreement only; not facially a conveyance; long description and effect absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>A85:K85</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2395/967-972; I-2022-004938</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>2395/967-972; I-2022-004938</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr">
+        <is>
+          <t>Financing-statement termination only; NOT a title conveyance. Diversified ABS conveyance is 2395/415.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>A86:K86</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2475/943-959</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>2475/943-959</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Corporate succession into Canvas Energy II; full 17-page filing controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>A87:K87</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2476/67-108</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>2476/67-108</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Canvas-derived collateral lien; NO release found in current search — apparently outstanding; verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>A88:K88</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2476/109-120</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>2476/109-120</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Companion financing statement; no termination found — apparently active; verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>A89:K89</t>
+        </is>
+      </c>
+      <c r="C188" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2480/903-909</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E188" s="2" t="inlineStr">
+        <is>
+          <t>2480/903-909</t>
+        </is>
+      </c>
+      <c r="F188" s="2" t="inlineStr">
+        <is>
+          <t>Corporate filing; no Section 32 legal indexed — title effect requires the filing itself.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>A90:K90</t>
+        </is>
+      </c>
+      <c r="C189" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2487/28-31</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E189" s="2" t="inlineStr">
+        <is>
+          <t>2487/28-31</t>
+        </is>
+      </c>
+      <c r="F189" s="2" t="inlineStr">
+        <is>
+          <t>Post-index-cutoff continuation record; an affidavit is not a conveyance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B190" s="2" t="inlineStr">
+        <is>
+          <t>A91:K91</t>
+        </is>
+      </c>
+      <c r="C190" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2490/469-470</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E190" s="2" t="inlineStr">
+        <is>
+          <t>2490/469-470</t>
+        </is>
+      </c>
+      <c r="F190" s="2" t="inlineStr">
+        <is>
+          <t>First of two filings after the visible index cutoff (OKCR continuation closed through 7/9/2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B191" s="2" t="inlineStr">
+        <is>
+          <t>A92:K92</t>
+        </is>
+      </c>
+      <c r="C191" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2490/471-473</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E191" s="2" t="inlineStr">
+        <is>
+          <t>2490/471-473</t>
+        </is>
+      </c>
+      <c r="F191" s="2" t="inlineStr">
+        <is>
+          <t>Current terminal record of the continuation (surface/fee context; not a leasehold instrument on its face — image controls).</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B192" s="2" t="inlineStr">
+        <is>
+          <t>A93:K93</t>
+        </is>
+      </c>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2168/35</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>2168/35</t>
+        </is>
+      </c>
+      <c r="F192" s="2" t="inlineStr">
+        <is>
+          <t>Companion Fortune-to-FourPoint input. Some transcriptions show page 44 — page discrepancy carried; the record controls.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B193" s="2" t="inlineStr">
+        <is>
+          <t>A94:K94</t>
+        </is>
+      </c>
+      <c r="C193" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2341/127</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E193" s="2" t="inlineStr">
+        <is>
+          <t>2341/127</t>
+        </is>
+      </c>
+      <c r="F193" s="2" t="inlineStr">
+        <is>
+          <t>Mortgage family referenced by the 2371/439 release — pull to confirm released collateral scope.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B194" s="2" t="inlineStr">
+        <is>
+          <t>A95:K95</t>
+        </is>
+      </c>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2389/590</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>2389/590</t>
+        </is>
+      </c>
+      <c r="F194" s="2" t="inlineStr">
+        <is>
+          <t>Mortgage referenced by the 2395/370 release — pull to confirm full release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>A96:K96</t>
+        </is>
+      </c>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2389/630</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>2389/630</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>Financing statement referenced by terminations 2395/967-972 and 2395/973.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B196" s="2" t="inlineStr">
+        <is>
+          <t>A97:K97</t>
+        </is>
+      </c>
+      <c r="C196" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2453/389-2455/700</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E196" s="2" t="inlineStr">
+        <is>
+          <t>2453/389-2455/700</t>
+        </is>
+      </c>
+      <c r="F196" s="2" t="inlineStr">
+        <is>
+          <t>Release family runs across continuation pages 2453/389 through 2455/700; companion termination runs 2455/705 through 2457/936. Separate from the MNR/UMB lien family.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B197" s="2" t="inlineStr">
+        <is>
+          <t>A98:K98</t>
+        </is>
+      </c>
+      <c r="C197" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2307/566; 2307/583; 2359/304; 2360/336</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E197" s="2" t="inlineStr">
+        <is>
+          <t>2307/566; 2307/583; 2359/304; 2360/336</t>
+        </is>
+      </c>
+      <c r="F197" s="2" t="inlineStr">
+        <is>
+          <t>SEPARATE CHAIN: 2019 Apache acquisition and BMO mortgage/2021 terminations. No record ties Presidio WAB to the drilled Carlson wells or any Diversified branch — do not blend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B198" s="2" t="inlineStr">
+        <is>
+          <t>A99:K99</t>
+        </is>
+      </c>
+      <c r="C198" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2317/613; 2377/765; 2416/49; 2424/175-530; 2446/1-232</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E198" s="2" t="inlineStr">
+        <is>
+          <t>2317/613; 2377/765; 2416/49; 2424/175-530; 2446/1-232</t>
+        </is>
+      </c>
+      <c r="F198" s="2" t="inlineStr">
+        <is>
+          <t>SEPARATE CHAIN: parallel BCE-Mach operator/title and financing cycle (operator of JGL, Hanks Crook, LeGrand, Twin wells). Do not blend with Diversified absent a recorded bridge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B199" s="2" t="inlineStr">
+        <is>
+          <t>A100:K100</t>
+        </is>
+      </c>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2378/143; 2380/403</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>2378/143; 2380/403</t>
+        </is>
+      </c>
+      <c r="F199" s="2" t="inlineStr">
+        <is>
+          <t>Origin of the 2022 JPMorgan/Unbridled lien family that the 2025 release/termination family (2453/389-2457/936) appears to clear. Match schedules before treating as cleared.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>A101:K101</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2415/237; 2417/1</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E200" s="2" t="inlineStr">
+        <is>
+          <t>2415/237; 2417/1</t>
+        </is>
+      </c>
+      <c r="F200" s="2" t="inlineStr">
+        <is>
+          <t>Additional filings in the 2023 Unbridled/MNR securitization sequence identified by the entity map; exact instrument types and effect require images.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>A102:K102</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2042/9</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E201" s="2" t="inlineStr">
+        <is>
+          <t>2042/9</t>
+        </is>
+      </c>
+      <c r="F201" s="2" t="inlineStr">
+        <is>
+          <t>Last record before the missing logical index page 48. The omitted interval runs from here to I-2012-001013.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>A103:K103</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>Retained Section 32 runsheet entry 2080/798-799</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>FV</t>
+        </is>
+      </c>
+      <c r="E202" s="2" t="inlineStr">
+        <is>
+          <t>2080/798-799</t>
+        </is>
+      </c>
+      <c r="F202" s="2" t="inlineStr">
+        <is>
+          <t>First logical-page-49 record after the missing page 48; high-resolution review confirms handwritten book 2080, consistent with OKCR metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>A104:K104</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 1016/7</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E203" s="2" t="inlineStr">
+        <is>
+          <t>1016 series; index lead, face not held</t>
+        </is>
+      </c>
+      <c r="F203" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>A105:K105</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 1016/13</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E204" s="2" t="inlineStr">
+        <is>
+          <t>1016 series; index lead, face not held</t>
+        </is>
+      </c>
+      <c r="F204" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>A106:K106</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 1016/18</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>1016 series; index lead, face not held</t>
+        </is>
+      </c>
+      <c r="F205" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>A107:K107</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 1016/25</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>1016 series; index lead, face not held</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>A108:K108</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 1016/29</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>1016 series; index lead, face not held</t>
+        </is>
+      </c>
+      <c r="F207" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>A109:K109</t>
+        </is>
+      </c>
+      <c r="C208" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 1016/33</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E208" s="2" t="inlineStr">
+        <is>
+          <t>1016 series; index lead, face not held</t>
+        </is>
+      </c>
+      <c r="F208" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B209" s="2" t="inlineStr">
+        <is>
+          <t>A110:K110</t>
+        </is>
+      </c>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 1016/90</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>1016 series; index lead, face not held</t>
+        </is>
+      </c>
+      <c r="F209" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B210" s="2" t="inlineStr">
+        <is>
+          <t>A111:K111</t>
+        </is>
+      </c>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 1697/236</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Recorded-face lead; required bridge into modern chain</t>
+        </is>
+      </c>
+      <c r="F210" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>A112:K112</t>
+        </is>
+      </c>
+      <c r="C211" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 2434/751</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E211" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL post-cutoff index lead; may convey the reported Diversified branch out</t>
+        </is>
+      </c>
+      <c r="F211" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B212" s="2" t="inlineStr">
+        <is>
+          <t>A113:K113</t>
+        </is>
+      </c>
+      <c r="C212" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 2451/4</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E212" s="2" t="inlineStr">
+        <is>
+          <t>Post-cutoff corporate filing; asset-specific effect unknown</t>
+        </is>
+      </c>
+      <c r="F212" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B213" s="2" t="inlineStr">
+        <is>
+          <t>A114:K114</t>
+        </is>
+      </c>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 2476/121</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Post-cutoff intra-family restructuring lead; schedule required</t>
+        </is>
+      </c>
+      <c r="F213" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>Runsheet</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>A115:K115</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>Added missing Section 32 chain lead 2480/824</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>V7, V10</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>Post-cutoff notice lead; recitals and asset effect unknown</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Locator/qualified evidence; full instrument required</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>Tract 1</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>A5:H5</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>PAT Patent 3/469 — Sovereign inception; no mineral reservation apparent</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>P-001 / Img 0003</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Tract 1</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>A6:H6</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>WD Roger Mills Co. 11/214 (pre-Beckham record) — Section 32 NE/4 fee; no reservation apparent</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>V7 direct-face register</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Tract 1</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>A7:H7</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>WD 10/255 — Fee to Adolf; downstream chain incomplete</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>V7 direct-face register</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Tract 1</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>A8:H8</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>DECR 83/259 — Collective mineral vesting; allocations require decree</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>V7 probate extraction</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="inlineStr">
+        <is>
+          <t>Tract 1</t>
+        </is>
+      </c>
+      <c r="B219" s="2" t="inlineStr">
+        <is>
+          <t>A9:H9</t>
+        </is>
+      </c>
+      <c r="C219" s="2" t="inlineStr">
+        <is>
+          <t>DECR 845/150-157 — Five 8-NMA estimated last-located interests</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="inlineStr">
+        <is>
+          <t>V7 probate extraction</t>
+        </is>
+      </c>
+      <c r="F219" s="2" t="inlineStr">
+        <is>
+          <t>High quantum / current status open</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="inlineStr">
+        <is>
+          <t>Tract 1</t>
+        </is>
+      </c>
+      <c r="B220" s="2" t="inlineStr">
+        <is>
+          <t>A10:H10</t>
+        </is>
+      </c>
+      <c r="C220" s="2" t="inlineStr">
+        <is>
+          <t>MD 92/47 — 1.5 NMA each per deed; later one grantee unextracted</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="inlineStr">
+        <is>
+          <t>V7 direct-face register</t>
+        </is>
+      </c>
+      <c r="F220" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="inlineStr">
+        <is>
+          <t>Tract 1</t>
+        </is>
+      </c>
+      <c r="B221" s="2" t="inlineStr">
+        <is>
+          <t>A11:H11</t>
+        </is>
+      </c>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>MD 367/632 — 10 NMA; competing 267/638 out-conveyance must be resolved</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>V7 direct-face register</t>
+        </is>
+      </c>
+      <c r="F221" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Tract 1</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>A12:H12</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>COVERAGE GAP OGL 332/74-75 — Lease face located, but lessor mineral vesting is not tied to the estimated NE/4 owner schedule</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>V10 lease-to-owner audit</t>
+        </is>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>High gap confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Tract 2</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>A5:H5</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>FR Final Receiver Receipt 3894 — Earliest located NW/4 evidence; patent not located</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>P-003 / Img 0005</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>90% identity / 0% patent</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Tract 2</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>A6:H6</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>STIP 153/161-162 — Recorded residual quantum used for estimated ending schedule</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>V7 title register</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>Medium-high</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Tract 2</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>A7:H7</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>MD/ORDER 85/363-366; 311/817-828 — Estimated last-located mineral interests</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>V7 title register</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Varies; current status open</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>Tract 2</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>A8:H8</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>DECR P-76-78 — Decree allocation incomplete; 13.333333-NMA residual assumed</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>V7 title register</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>Tract 2</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>A9:H9</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>OGL 340/323 — N/2 NW/4 plus N/2 SW/4; no current HBP conclusion</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Direct face</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>High terms / open status</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>Tract 3</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>A5:H5</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>FR Final Receiver Receipt 3895 — Earliest located SW/4 evidence; patent not located</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>P-004 / Img 0006</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>90% identity / 0% patent</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>Tract 3</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>A6:H6</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>MD 81/194 — 40 NMA in S/2 SW/4 ending schedule</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>V7 title register</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Medium; current status open</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Tract 3</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>A7:H7</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>MD/DECR 85/222; 262/490-493 — Estimated last-located interests</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>V7 title register</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Tract 3</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>A8:H8</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>OGL 340/302; 340/304; 342/564; 342/566 — Overlapping N/2 SW/4 leases; not additive</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Direct faces</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>High terms / open status</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>Tract 3</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>A9:H9</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>ASG 872/279 — Top Morrow-19,480 ft; ORRIs reserved; modern bridge open</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Direct images</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>98% historic / open current</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Tract 4</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>A5:H5</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>FR Final Receiver Receipt — Earliest located SE/4 evidence; Biggs/Bigge patent remains missing</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>P-002 / Img 0004</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>90% identity / 0% patent</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Tract 4</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>A6:H6</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>OGL 63/33 — E/2 SE/4, 1/8 royalty, 10-year term; present status open</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Direct face</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>98% terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Tract 4</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>A7:H7</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>ASG 244/432 — Historic 63/33 assignment branch</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>Direct image</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>96%</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Tract 4</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>A8:H8</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>WB ASG 845/47 — Pearl wellbore 11,100-19,480 ft; 1/8 ORRI</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>Direct image</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>98% historic</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Tract 4</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>A9:H9</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>OGL 307/31 — W/2 SE/4 and S/2 SW/4; present status open</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>Direct face</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>98% terms</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Tract 5</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>A5:H5</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>ASG 1697/236 — Scheduled predecessor lead; full Exhibit A controls</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>Recorded face / Exhibit A required</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Tract 5</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>A6:H6</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>ASG 2340/490 — Full-section indexed; missing Tapstone/asset bridge schedules</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>Index / schedule missing</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>High metadata / low scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Tract 5</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>A7:H7</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>ASG 2371/470-494 — 51.25%/48.75% transaction branches; not current WI</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Index / instrument partial</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>High parties / low asset quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Tract 5</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>A8:H8</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>MERGER 2389/500-580 — Corporate consolidation; asset-specific effect open</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>Index / certificate missing</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>High metadata</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Tract 5</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>A9:H9</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>CONV 2395/415-464 — OK48147.001.1 identified; allocation/estate/depth blank</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed asset line 2395/462</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>High asset identity / low quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Tract 5</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>A10:H10</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>CONV 2400/551-567 — Last claimant supported by reviewed schedule; not confirmed current</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Reviewed asset line 2400/566</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>High asset identity / low quantum</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Tract 5</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>A11:H11</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>ASG LEAD 2434/751 — CRITICAL: if Section 32/OK48147.001.1 is scheduled, Diversified's branch was conveyed out</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>V10 county-index lead; face unread</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>High parties / unknown coverage</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Tract 5</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>A12:H12</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>AGMT 2476/121-130 — Agreement, not facial conveyance; current vesting effect open</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>Index/public metadata</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>High metadata / low title effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>WI 1</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>A5:H5</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Historic scheduled predecessor lead</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>LC, V7, V10, FV</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>1697/236</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Full Exhibit A required</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>WI 1</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>A6:H6</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Potential bridge branch</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>LC, V7, V10, FV</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>2340/403</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Missing Tapstone schedule/bridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>WI 1</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>A7:H7</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Principal indexed predecessor</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>LC, V7, V10, FV</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>2340/490</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Asset schedule absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>WI 1</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>A8:H8</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Keep branches separate</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>LC, V7, V10, FV</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>2371/470-494</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Not current Section 32 WI</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>WI 1</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>A9:H9</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Merger path</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>LC, V7, V10, FV</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>2389/500-580</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>Certificate and schedules absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>WI 1</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>A10:H10</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Asset identity supported</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>LC, V7, V10, FV</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>2395/415-464</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Estate/depth/quantum blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>WI 1</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>A11:H11</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Last claimant supported by reviewed schedule</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>LC, V7, V10, FV</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>2400/551-567</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Not confirmed current; later filings control</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>WI 1</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>A12:H12</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>Potential conveyance out</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>LC, V7, V10, FV</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>2434/751</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL — read first</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>WI 1</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>A13:H13</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Later context only</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>LC, V7, V10, FV</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>2451/4; 2476/121; 2480/824</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Read complete instruments and schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>WI 2</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>A5:H5</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Historic only; survival open</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>502/267</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Payout, reversion and releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>WI 2</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>A6:H6</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Historic allocation only</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>509/220</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Prove baseline and successors</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>WI 2</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>A7:H7</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Historic only; status open</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>845/47</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>Read unrecorded agreement and releases</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>WI 2</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>A8:H8</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Historic only; bridge open</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>872/279</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Complete instrument and 1984 agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>WI 2</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>A9:H9</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Nemo-dat/source-title defect</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>1014/75</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Prove assignor WI source</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>WI 2</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>A10:H10</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>Separate branch; do not blend</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>2183/174; 2185/639</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Read complete exhibits and legal</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>WI 2</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>A11:H11</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>Parallel portfolio branch</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>FV, V7, V10, MT</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>2185/639; 2225/1; 2415/328</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Reconcile Teocalli carve and schedules</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
           <t>Well 1</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>A3:Q3</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Cora Garrett C-310 / 35-009-00075</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>A4:Q4</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>Crook 1-32 / 35-009-20312</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>No rolling-12-month OTC rows (PUN 009-066620-0-0000, Active, 640 ac, still lists BP). AC/DRY under Complete Oil &amp; Gas Services LLC; Latigo-to-Complete Form 1073MW approved 12/3/2025 (Crook first of 38 wells). AC proves an open wellbore — NOT production or HBP.</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>A5:Q5</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Pearl 1-32 / 35-009-20605</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>A6:Q6</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Legrand 1-32 / 35-009-20738</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>A7:Q7</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>JGL 1-32 / 35-009-21072</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Gas reported 7/2025-4/2026; 4/2026 = 2,367 MCF (OTC PUN 009-101800-0-0000, reported by NextEra Energy Marketing). Production fact only — HBP not concluded.</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>A8:Q8</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>Hanks Crook 1-32 / 35-009-21085</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Active PUN returned no rolling-12-month rows on 7/9/2026.</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>A9:Q9</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>Crook-Legrand 1-32 / 35-009-21166</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>A10:Q10</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>Legrand 1-32 / 35-009-21236</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E269" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F269" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>A11:Q11</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>Katie 1-32 / 35-009-21245</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E270" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F270" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>A12:Q12</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>Legrand 2-32 / 35-009-21258</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E271" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F271" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>A13:Q13</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>Twin 1-32 / 35-009-21391</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E272" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="F272" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>A14:Q14</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>Carlson 32-11-25 12H / 35-009-21893</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E273" s="2" t="inlineStr">
+        <is>
+          <t>Gas through 5/2026; 5/2026 = 2,113 MCF (OTC PUN 009-211663-0-0000, Active, 640 ac). OTC displays API 009-21903 on this PUN — that API belongs to the permit-only Riviera 9H (approved 10/2/2013, expired 4/2/2014); conflict carried. Operator chain per official OCC forms: Linn → EnerVest → BP → Latigo.</t>
+        </is>
+      </c>
+      <c r="F273" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>A15:Q15</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>Carlson 32-11-25 7H / 35-009-21923</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>FV official OCC/OTC synthesis; V10 well register</t>
+        </is>
+      </c>
+      <c r="E274" s="2" t="inlineStr">
+        <is>
+          <t>Historic completion facts only — not proof of current production, lease HBP or title.</t>
+        </is>
+      </c>
+      <c r="F274" s="2" t="inlineStr">
+        <is>
+          <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
+        <is>
+          <t>Well 1</t>
+        </is>
+      </c>
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>A16:Q16</t>
         </is>
       </c>
-      <c r="C166" s="2" t="inlineStr">
+      <c r="C275" s="2" t="inlineStr">
         <is>
           <t>Carlson 32-11-25 10H / 35-009-21933</t>
         </is>
       </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>FV official OCC/OTC synthesis; V10 well register</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>Historic completion facts only — not proof of current production, lease HBP or title.</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>Operator/status are regulatory context only; lease-specific HBP not independently confirmed</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F166"/>
+  <autoFilter ref="A1:F275"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6342,7 +9830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6505,7 +9993,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Diversified Production LLC is the latest supported named claimant, not a proven 640-acre/100% owner.</t>
+          <t>Diversified is the last claimant supported by the reviewed 2400 schedule, not a confirmed current or 640-acre/100% owner.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -6700,6 +10188,60 @@
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Map each operative modern schedule lease-by-lease.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>C-13</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Bk 2434/751 may convey Diversified/DP Legacy Central interests to Teocalli after the reviewed-title cutoff.</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>V10 county-index lead; recorded face and schedule unavailable</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Diversified is described only as the last claimant supported by the reviewed 2400 schedule. Current claimant status is expressly unconfirmed.</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>CRITICAL — read 2434/751 first and determine whether Section 32/OK48147.001.1 is included.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>C-14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Viersen OGL 332/74-75 has no lessor-mineral vesting crosswalk to the estimated NE/4 owners.</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>V10 lease-to-owner coverage audit; OGL face reviewed</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Coverage gap is visible on OGL and Tract 1; no current leasehold conclusion is drawn.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Establish Viersen lessor vesting and reconcile it to the NE/4 title schedule.</t>
         </is>
       </c>
     </row>
